--- a/WP_Aset tetap_TAM 2026.xlsx
+++ b/WP_Aset tetap_TAM 2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="21126"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\DROPBOX\DAGAB\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BTV\debug\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3EB7BF5-283F-49FB-8929-D7609EDF536B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E777ACE-3575-4D91-BE5B-B901EE98CA3E}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9048" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Kendaraan" sheetId="4" r:id="rId1"/>
@@ -3058,6 +3058,18 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3134,18 +3146,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="38" fontId="4" fillId="0" borderId="4" xfId="13" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="15" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -3549,59 +3549,59 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B1:BR98"/>
-  <sheetFormatPr defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="23" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" style="23" customWidth="1"/>
-    <col min="5" max="5" width="2.83203125" customWidth="1"/>
-    <col min="6" max="6" width="35.1640625" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" customWidth="1"/>
-    <col min="8" max="8" width="15.33203125" style="24" customWidth="1"/>
-    <col min="9" max="9" width="17.5" style="25" customWidth="1"/>
-    <col min="10" max="10" width="16.83203125" style="25" customWidth="1"/>
-    <col min="11" max="11" width="15.6640625" style="25" customWidth="1"/>
-    <col min="12" max="15" width="18.5" style="25" customWidth="1"/>
-    <col min="16" max="19" width="7.83203125" customWidth="1"/>
-    <col min="20" max="20" width="8.33203125" customWidth="1"/>
-    <col min="21" max="23" width="7.83203125" customWidth="1"/>
-    <col min="24" max="24" width="10.83203125" style="25" customWidth="1"/>
+    <col min="1" max="1" width="2.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="23" customWidth="1"/>
+    <col min="5" max="5" width="2.85546875" customWidth="1"/>
+    <col min="6" max="6" width="35.140625" customWidth="1"/>
+    <col min="7" max="7" width="13.28515625" customWidth="1"/>
+    <col min="8" max="8" width="15.28515625" style="24" customWidth="1"/>
+    <col min="9" max="9" width="17.42578125" style="25" customWidth="1"/>
+    <col min="10" max="10" width="16.85546875" style="25" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="25" customWidth="1"/>
+    <col min="12" max="15" width="18.42578125" style="25" customWidth="1"/>
+    <col min="16" max="19" width="7.85546875" customWidth="1"/>
+    <col min="20" max="20" width="8.28515625" customWidth="1"/>
+    <col min="21" max="23" width="7.85546875" customWidth="1"/>
+    <col min="24" max="24" width="10.85546875" style="25" customWidth="1"/>
     <col min="25" max="25" width="15" style="25" customWidth="1"/>
-    <col min="26" max="26" width="8.5" customWidth="1"/>
-    <col min="27" max="27" width="8.33203125" customWidth="1"/>
+    <col min="26" max="26" width="8.42578125" customWidth="1"/>
+    <col min="27" max="27" width="8.28515625" customWidth="1"/>
     <col min="28" max="30" width="16" customWidth="1"/>
-    <col min="31" max="31" width="8.5" customWidth="1"/>
-    <col min="32" max="32" width="8.1640625" customWidth="1"/>
+    <col min="31" max="31" width="8.42578125" customWidth="1"/>
+    <col min="32" max="32" width="8.140625" customWidth="1"/>
     <col min="33" max="35" width="16" customWidth="1"/>
-    <col min="36" max="36" width="9.33203125" customWidth="1"/>
-    <col min="37" max="37" width="8.33203125" customWidth="1"/>
-    <col min="38" max="38" width="14.5" customWidth="1"/>
-    <col min="39" max="39" width="16.1640625" customWidth="1"/>
+    <col min="36" max="36" width="9.28515625" customWidth="1"/>
+    <col min="37" max="37" width="8.28515625" customWidth="1"/>
+    <col min="38" max="38" width="14.42578125" customWidth="1"/>
+    <col min="39" max="39" width="16.140625" customWidth="1"/>
     <col min="40" max="40" width="16" customWidth="1"/>
     <col min="41" max="42" width="8" customWidth="1"/>
-    <col min="43" max="43" width="16.83203125" customWidth="1"/>
-    <col min="44" max="44" width="17.33203125" customWidth="1"/>
-    <col min="45" max="45" width="18.1640625" customWidth="1"/>
-    <col min="46" max="46" width="9.1640625" customWidth="1"/>
-    <col min="47" max="47" width="7.83203125" customWidth="1"/>
-    <col min="48" max="50" width="18.1640625" customWidth="1"/>
-    <col min="51" max="51" width="1.5" customWidth="1"/>
-    <col min="52" max="52" width="14.1640625" customWidth="1"/>
-    <col min="53" max="53" width="13.1640625" customWidth="1"/>
-    <col min="54" max="54" width="13.33203125" customWidth="1"/>
-    <col min="55" max="56" width="13.1640625" customWidth="1"/>
-    <col min="57" max="57" width="12.83203125" customWidth="1"/>
+    <col min="43" max="43" width="16.85546875" customWidth="1"/>
+    <col min="44" max="44" width="17.28515625" customWidth="1"/>
+    <col min="45" max="45" width="18.140625" customWidth="1"/>
+    <col min="46" max="46" width="9.140625" customWidth="1"/>
+    <col min="47" max="47" width="7.85546875" customWidth="1"/>
+    <col min="48" max="50" width="18.140625" customWidth="1"/>
+    <col min="51" max="51" width="1.42578125" customWidth="1"/>
+    <col min="52" max="52" width="14.140625" customWidth="1"/>
+    <col min="53" max="53" width="13.140625" customWidth="1"/>
+    <col min="54" max="54" width="13.28515625" customWidth="1"/>
+    <col min="55" max="56" width="13.140625" customWidth="1"/>
+    <col min="57" max="57" width="12.85546875" customWidth="1"/>
     <col min="58" max="58" width="13" customWidth="1"/>
-    <col min="59" max="59" width="12.83203125" customWidth="1"/>
-    <col min="60" max="60" width="13.1640625" customWidth="1"/>
+    <col min="59" max="59" width="12.85546875" customWidth="1"/>
+    <col min="60" max="60" width="13.140625" customWidth="1"/>
     <col min="61" max="61" width="13" customWidth="1"/>
-    <col min="62" max="62" width="13.5" customWidth="1"/>
-    <col min="63" max="63" width="13.6640625" customWidth="1"/>
-    <col min="64" max="64" width="14.5" customWidth="1"/>
+    <col min="62" max="62" width="13.42578125" customWidth="1"/>
+    <col min="63" max="63" width="13.7109375" customWidth="1"/>
+    <col min="64" max="64" width="14.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:70" ht="11.25" thickBot="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:70" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:70" ht="10.8" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:70" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="14" t="s">
         <v>22</v>
       </c>
@@ -3659,7 +3659,7 @@
       <c r="AW2" s="2"/>
       <c r="AX2" s="2"/>
     </row>
-    <row r="3" spans="2:70" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:70" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>23</v>
       </c>
@@ -3716,7 +3716,7 @@
       <c r="AW3" s="34"/>
       <c r="AX3" s="34"/>
     </row>
-    <row r="4" spans="2:70" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:70" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -3773,51 +3773,51 @@
       <c r="AW4" s="2"/>
       <c r="AX4" s="2"/>
     </row>
-    <row r="6" spans="2:70" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:70" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="391" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="398" t="s">
+      <c r="C6" s="402" t="s">
         <v>29</v>
       </c>
       <c r="D6" s="41"/>
-      <c r="E6" s="399" t="s">
+      <c r="E6" s="403" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="400"/>
-      <c r="G6" s="405" t="s">
+      <c r="F6" s="404"/>
+      <c r="G6" s="409" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="406"/>
-      <c r="I6" s="409" t="s">
+      <c r="H6" s="410"/>
+      <c r="I6" s="413" t="s">
         <v>12</v>
       </c>
-      <c r="J6" s="409"/>
-      <c r="K6" s="409"/>
-      <c r="L6" s="409"/>
-      <c r="M6" s="414" t="s">
+      <c r="J6" s="413"/>
+      <c r="K6" s="413"/>
+      <c r="L6" s="413"/>
+      <c r="M6" s="418" t="s">
         <v>32</v>
       </c>
-      <c r="N6" s="415"/>
-      <c r="O6" s="416"/>
-      <c r="P6" s="417" t="s">
+      <c r="N6" s="419"/>
+      <c r="O6" s="420"/>
+      <c r="P6" s="421" t="s">
         <v>33</v>
       </c>
-      <c r="Q6" s="418"/>
-      <c r="R6" s="418"/>
-      <c r="S6" s="419"/>
-      <c r="T6" s="420" t="s">
+      <c r="Q6" s="422"/>
+      <c r="R6" s="422"/>
+      <c r="S6" s="423"/>
+      <c r="T6" s="396" t="s">
         <v>34</v>
       </c>
-      <c r="U6" s="421"/>
-      <c r="V6" s="420" t="s">
+      <c r="U6" s="397"/>
+      <c r="V6" s="396" t="s">
         <v>35</v>
       </c>
-      <c r="W6" s="421"/>
-      <c r="X6" s="394" t="s">
+      <c r="W6" s="397"/>
+      <c r="X6" s="398" t="s">
         <v>36</v>
       </c>
-      <c r="Y6" s="395"/>
+      <c r="Y6" s="399"/>
       <c r="Z6" s="279"/>
       <c r="AA6" s="390">
         <v>44926</v>
@@ -3854,60 +3854,60 @@
       <c r="AW6" s="390"/>
       <c r="AX6" s="390"/>
     </row>
-    <row r="7" spans="2:70" s="6" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:70" s="6" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="391"/>
-      <c r="C7" s="398"/>
+      <c r="C7" s="402"/>
       <c r="D7" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="401"/>
-      <c r="F7" s="402"/>
-      <c r="G7" s="407"/>
-      <c r="H7" s="408"/>
-      <c r="I7" s="410">
+      <c r="E7" s="405"/>
+      <c r="F7" s="406"/>
+      <c r="G7" s="411"/>
+      <c r="H7" s="412"/>
+      <c r="I7" s="414">
         <v>43100</v>
       </c>
-      <c r="J7" s="411" t="s">
+      <c r="J7" s="415" t="s">
         <v>38</v>
       </c>
-      <c r="K7" s="411" t="s">
+      <c r="K7" s="415" t="s">
         <v>39</v>
       </c>
       <c r="L7" s="44">
         <v>43465</v>
       </c>
-      <c r="M7" s="411" t="s">
+      <c r="M7" s="415" t="s">
         <v>8</v>
       </c>
-      <c r="N7" s="411" t="s">
+      <c r="N7" s="415" t="s">
         <v>9</v>
       </c>
       <c r="O7" s="44">
         <f>L7</f>
         <v>43465</v>
       </c>
-      <c r="P7" s="412" t="s">
+      <c r="P7" s="416" t="s">
         <v>40</v>
       </c>
-      <c r="Q7" s="413"/>
-      <c r="R7" s="412" t="s">
+      <c r="Q7" s="417"/>
+      <c r="R7" s="416" t="s">
         <v>41</v>
       </c>
-      <c r="S7" s="413"/>
-      <c r="T7" s="422" t="s">
+      <c r="S7" s="417"/>
+      <c r="T7" s="394" t="s">
         <v>42</v>
       </c>
-      <c r="U7" s="422" t="s">
+      <c r="U7" s="394" t="s">
         <v>43</v>
       </c>
-      <c r="V7" s="422" t="s">
+      <c r="V7" s="394" t="s">
         <v>42</v>
       </c>
-      <c r="W7" s="422" t="s">
+      <c r="W7" s="394" t="s">
         <v>43</v>
       </c>
-      <c r="X7" s="396"/>
-      <c r="Y7" s="397"/>
+      <c r="X7" s="400"/>
+      <c r="Y7" s="401"/>
       <c r="Z7" s="280"/>
       <c r="AA7" s="391" t="s">
         <v>44</v>
@@ -4014,26 +4014,26 @@
       </c>
       <c r="BM7" s="7"/>
     </row>
-    <row r="8" spans="2:70" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="391"/>
-      <c r="C8" s="398"/>
+      <c r="C8" s="402"/>
       <c r="D8" s="45"/>
-      <c r="E8" s="403"/>
-      <c r="F8" s="404"/>
+      <c r="E8" s="407"/>
+      <c r="F8" s="408"/>
       <c r="G8" s="46" t="s">
         <v>40</v>
       </c>
       <c r="H8" s="47" t="s">
         <v>41</v>
       </c>
-      <c r="I8" s="411"/>
-      <c r="J8" s="411"/>
-      <c r="K8" s="411"/>
+      <c r="I8" s="415"/>
+      <c r="J8" s="415"/>
+      <c r="K8" s="415"/>
       <c r="L8" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="M8" s="411"/>
-      <c r="N8" s="411"/>
+      <c r="M8" s="415"/>
+      <c r="N8" s="415"/>
       <c r="O8" s="48" t="s">
         <v>11</v>
       </c>
@@ -4049,10 +4049,10 @@
       <c r="S8" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="T8" s="423"/>
-      <c r="U8" s="423"/>
-      <c r="V8" s="423"/>
-      <c r="W8" s="423"/>
+      <c r="T8" s="395"/>
+      <c r="U8" s="395"/>
+      <c r="V8" s="395"/>
+      <c r="W8" s="395"/>
       <c r="X8" s="50" t="s">
         <v>40</v>
       </c>
@@ -4100,7 +4100,7 @@
       <c r="BK8" s="199"/>
       <c r="BL8" s="199"/>
     </row>
-    <row r="9" spans="2:70" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:70" x14ac:dyDescent="0.2">
       <c r="B9" s="52"/>
       <c r="C9" s="53"/>
       <c r="D9" s="54"/>
@@ -4151,7 +4151,7 @@
       <c r="AW9" s="367"/>
       <c r="AX9" s="367"/>
     </row>
-    <row r="10" spans="2:70" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:70" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B10" s="61"/>
       <c r="C10" s="62" t="s">
         <v>5</v>
@@ -4217,7 +4217,7 @@
       <c r="BK10" s="206"/>
       <c r="BL10" s="206"/>
     </row>
-    <row r="11" spans="2:70" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:70" x14ac:dyDescent="0.2">
       <c r="B11" s="68"/>
       <c r="C11" s="69"/>
       <c r="D11" s="70"/>
@@ -4281,7 +4281,7 @@
       <c r="BK11" s="201"/>
       <c r="BL11" s="201"/>
     </row>
-    <row r="12" spans="2:70" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:70" x14ac:dyDescent="0.2">
       <c r="B12" s="75"/>
       <c r="C12" s="76">
         <v>41243</v>
@@ -4480,7 +4480,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:70" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:70" x14ac:dyDescent="0.2">
       <c r="B13" s="75"/>
       <c r="C13" s="370">
         <v>41243</v>
@@ -4675,7 +4675,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:70" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:70" x14ac:dyDescent="0.2">
       <c r="B14" s="75"/>
       <c r="C14" s="370">
         <v>41243</v>
@@ -4870,7 +4870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:70" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:70" x14ac:dyDescent="0.2">
       <c r="B15" s="75"/>
       <c r="C15" s="329">
         <v>41248</v>
@@ -5061,7 +5061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:70" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:70" x14ac:dyDescent="0.2">
       <c r="B16" s="75"/>
       <c r="C16" s="76">
         <v>41320</v>
@@ -5265,7 +5265,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="17" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B17" s="75"/>
       <c r="C17" s="76">
         <v>41339</v>
@@ -5466,7 +5466,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B18" s="75"/>
       <c r="C18" s="76">
         <v>42727</v>
@@ -5682,7 +5682,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B19" s="68"/>
       <c r="C19" s="89"/>
       <c r="D19" s="70"/>
@@ -5746,7 +5746,7 @@
       <c r="BK19" s="201"/>
       <c r="BL19" s="201"/>
     </row>
-    <row r="20" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B20" s="68"/>
       <c r="C20" s="89">
         <v>42830</v>
@@ -5964,7 +5964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B21" s="68"/>
       <c r="C21" s="89">
         <v>42940</v>
@@ -6182,7 +6182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B22" s="68"/>
       <c r="C22" s="89">
         <v>42998</v>
@@ -6400,7 +6400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B23" s="68"/>
       <c r="C23" s="89">
         <v>42998</v>
@@ -6618,7 +6618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B24" s="68"/>
       <c r="C24" s="89">
         <v>43026</v>
@@ -6836,7 +6836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B25" s="68"/>
       <c r="C25" s="89">
         <v>43046</v>
@@ -7054,7 +7054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:64" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:64" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="97"/>
       <c r="C26" s="257">
         <v>43143</v>
@@ -7270,7 +7270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:64" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:64" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B27" s="97"/>
       <c r="C27" s="257">
         <v>43353</v>
@@ -7486,7 +7486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B28" s="68"/>
       <c r="C28" s="89"/>
       <c r="D28" s="70"/>
@@ -7550,7 +7550,7 @@
       <c r="BK28" s="201"/>
       <c r="BL28" s="201"/>
     </row>
-    <row r="29" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B29" s="68"/>
       <c r="C29" s="257">
         <v>44773</v>
@@ -7755,7 +7755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B30" s="68"/>
       <c r="C30" s="257">
         <v>44837</v>
@@ -7963,7 +7963,7 @@
         <v>5477068.75</v>
       </c>
     </row>
-    <row r="31" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B31" s="68"/>
       <c r="C31" s="257">
         <v>44868</v>
@@ -8171,7 +8171,7 @@
         <v>5477068.75</v>
       </c>
     </row>
-    <row r="32" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B32" s="68"/>
       <c r="C32" s="257">
         <v>44917</v>
@@ -8379,7 +8379,7 @@
         <v>8215603.125</v>
       </c>
     </row>
-    <row r="33" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B33" s="68"/>
       <c r="C33" s="257"/>
       <c r="D33" s="70"/>
@@ -8443,7 +8443,7 @@
       <c r="BK33" s="201"/>
       <c r="BL33" s="201"/>
     </row>
-    <row r="34" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B34" s="68"/>
       <c r="C34" s="89"/>
       <c r="D34" s="70"/>
@@ -8491,7 +8491,7 @@
       <c r="AX34" s="253"/>
       <c r="AZ34" s="301"/>
     </row>
-    <row r="35" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B35" s="68"/>
       <c r="C35" s="89"/>
       <c r="D35" s="70"/>
@@ -8645,7 +8645,7 @@
         <v>19169740.625</v>
       </c>
     </row>
-    <row r="36" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B36" s="68"/>
       <c r="C36" s="89"/>
       <c r="D36" s="70"/>
@@ -8709,7 +8709,7 @@
       <c r="BK36" s="201"/>
       <c r="BL36" s="201"/>
     </row>
-    <row r="37" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B37" s="68"/>
       <c r="C37" s="257">
         <v>45463</v>
@@ -8895,7 +8895,7 @@
         <v>314504.15625</v>
       </c>
     </row>
-    <row r="38" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B38" s="68"/>
       <c r="C38" s="257">
         <v>45642</v>
@@ -9081,7 +9081,7 @@
         <v>6376487.145833333</v>
       </c>
     </row>
-    <row r="39" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B39" s="68"/>
       <c r="C39" s="257">
         <v>45642</v>
@@ -9267,7 +9267,7 @@
         <v>2945421.6458333335</v>
       </c>
     </row>
-    <row r="40" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B40" s="68"/>
       <c r="C40" s="257">
         <v>45642</v>
@@ -9453,7 +9453,7 @@
         <v>2455725.3958333335</v>
       </c>
     </row>
-    <row r="41" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B41" s="68"/>
       <c r="C41" s="257"/>
       <c r="D41" s="70"/>
@@ -9518,7 +9518,7 @@
       <c r="BK41" s="203"/>
       <c r="BL41" s="203"/>
     </row>
-    <row r="42" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B42" s="68"/>
       <c r="C42" s="257"/>
       <c r="D42" s="70"/>
@@ -9655,7 +9655,7 @@
         <v>12092138.34375</v>
       </c>
     </row>
-    <row r="43" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B43" s="68"/>
       <c r="C43" s="257"/>
       <c r="D43" s="70"/>
@@ -9720,7 +9720,7 @@
       <c r="BK43" s="118"/>
       <c r="BL43" s="118"/>
     </row>
-    <row r="44" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B44" s="68"/>
       <c r="C44" s="257">
         <v>45799</v>
@@ -9895,7 +9895,7 @@
         <v>298661.78125</v>
       </c>
     </row>
-    <row r="45" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B45" s="68"/>
       <c r="C45" s="257">
         <v>45883</v>
@@ -10070,7 +10070,7 @@
         <v>4824237.59375</v>
       </c>
     </row>
-    <row r="46" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B46" s="68"/>
       <c r="C46" s="257"/>
       <c r="D46" s="70"/>
@@ -10135,7 +10135,7 @@
       <c r="BK46" s="118"/>
       <c r="BL46" s="118"/>
     </row>
-    <row r="47" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B47" s="68"/>
       <c r="C47" s="257"/>
       <c r="D47" s="70"/>
@@ -10263,7 +10263,7 @@
         <v>5122899.375</v>
       </c>
     </row>
-    <row r="48" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B48" s="68"/>
       <c r="C48" s="257"/>
       <c r="D48" s="70"/>
@@ -10328,7 +10328,7 @@
       <c r="BK48" s="118"/>
       <c r="BL48" s="118"/>
     </row>
-    <row r="49" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B49" s="68"/>
       <c r="C49" s="257"/>
       <c r="D49" s="70"/>
@@ -10392,7 +10392,7 @@
       <c r="BK49" s="74"/>
       <c r="BL49" s="74"/>
     </row>
-    <row r="50" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B50" s="68"/>
       <c r="C50" s="257"/>
       <c r="D50" s="70"/>
@@ -10525,7 +10525,7 @@
         <v>36384778.34375</v>
       </c>
     </row>
-    <row r="51" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B51" s="68"/>
       <c r="C51" s="257"/>
       <c r="D51" s="70"/>
@@ -10589,7 +10589,7 @@
       <c r="BK51" s="201"/>
       <c r="BL51" s="201"/>
     </row>
-    <row r="52" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B52" s="68"/>
       <c r="C52" s="89"/>
       <c r="D52" s="70"/>
@@ -10653,7 +10653,7 @@
       <c r="BK52" s="201"/>
       <c r="BL52" s="201"/>
     </row>
-    <row r="53" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B53" s="68"/>
       <c r="C53" s="89"/>
       <c r="D53" s="70"/>
@@ -10717,7 +10717,7 @@
       <c r="BK53" s="201"/>
       <c r="BL53" s="201"/>
     </row>
-    <row r="54" spans="2:64" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:64" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B54" s="112"/>
       <c r="C54" s="113"/>
       <c r="D54" s="114"/>
@@ -10783,7 +10783,7 @@
       <c r="BK54" s="200"/>
       <c r="BL54" s="200"/>
     </row>
-    <row r="55" spans="2:64" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:64" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B55" s="126"/>
       <c r="C55" s="127">
         <v>39520</v>
@@ -10936,7 +10936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B56" s="126"/>
       <c r="C56" s="127">
         <v>40522</v>
@@ -11134,7 +11134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B57" s="126"/>
       <c r="C57" s="127">
         <v>40522</v>
@@ -11286,7 +11286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B58" s="126"/>
       <c r="C58" s="127">
         <v>40522</v>
@@ -11438,7 +11438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B59" s="126"/>
       <c r="C59" s="127">
         <v>40522</v>
@@ -11590,7 +11590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B60" s="126"/>
       <c r="C60" s="127">
         <v>42048</v>
@@ -11776,7 +11776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:64" x14ac:dyDescent="0.2">
       <c r="B61" s="140"/>
       <c r="C61" s="141"/>
       <c r="D61" s="142"/>
@@ -11840,7 +11840,7 @@
       <c r="BK61" s="204"/>
       <c r="BL61" s="204"/>
     </row>
-    <row r="62" spans="2:64" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:64" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B62" s="9"/>
       <c r="C62" s="155"/>
       <c r="D62" s="156"/>
@@ -12000,7 +12000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:64" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:64" x14ac:dyDescent="0.2">
       <c r="E63" s="165"/>
       <c r="H63" s="166"/>
       <c r="P63" s="167"/>
@@ -12035,7 +12035,7 @@
       <c r="AW63" s="25"/>
       <c r="AX63" s="25"/>
     </row>
-    <row r="64" spans="2:64" ht="11.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="64" spans="2:64" ht="10.8" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E64" s="165"/>
       <c r="H64" s="166"/>
       <c r="L64" s="193">
@@ -12171,7 +12171,7 @@
         <v>36384778.34375</v>
       </c>
     </row>
-    <row r="65" spans="2:53" ht="11.25" thickTop="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:53" ht="10.8" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B65" s="10" t="s">
         <v>65</v>
       </c>
@@ -12210,7 +12210,7 @@
       <c r="AX65" s="25"/>
       <c r="AZ65" s="172"/>
     </row>
-    <row r="66" spans="2:53" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:53" x14ac:dyDescent="0.2">
       <c r="B66" s="10"/>
       <c r="E66" s="165"/>
       <c r="H66" s="166"/>
@@ -12258,7 +12258,7 @@
       <c r="AZ66" s="225"/>
       <c r="BA66" s="172"/>
     </row>
-    <row r="67" spans="2:53" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:53" x14ac:dyDescent="0.2">
       <c r="C67" s="173" t="s">
         <v>12</v>
       </c>
@@ -12306,7 +12306,7 @@
       <c r="AW67" s="25"/>
       <c r="AX67" s="25"/>
     </row>
-    <row r="68" spans="2:53" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:53" x14ac:dyDescent="0.2">
       <c r="C68" s="172" t="s">
         <v>46</v>
       </c>
@@ -12343,7 +12343,7 @@
       <c r="AW68" s="25"/>
       <c r="AX68" s="25"/>
     </row>
-    <row r="69" spans="2:53" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:53" x14ac:dyDescent="0.2">
       <c r="C69" s="172" t="s">
         <v>66</v>
       </c>
@@ -12391,7 +12391,7 @@
       <c r="AW69" s="319"/>
       <c r="AX69" s="319"/>
     </row>
-    <row r="70" spans="2:53" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:53" x14ac:dyDescent="0.2">
       <c r="C70" s="172"/>
       <c r="E70" s="165"/>
       <c r="H70" s="175"/>
@@ -12434,7 +12434,7 @@
       <c r="AW70" s="25"/>
       <c r="AX70" s="25"/>
     </row>
-    <row r="71" spans="2:53" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:53" x14ac:dyDescent="0.2">
       <c r="E71" s="165"/>
       <c r="H71" s="166"/>
       <c r="L71" s="343">
@@ -12476,7 +12476,7 @@
       <c r="AW71" s="25"/>
       <c r="AX71" s="25"/>
     </row>
-    <row r="72" spans="2:53" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:53" x14ac:dyDescent="0.2">
       <c r="E72" s="165"/>
       <c r="H72" s="166"/>
       <c r="L72" s="343">
@@ -12515,7 +12515,7 @@
       <c r="AW72" s="25"/>
       <c r="AX72" s="25"/>
     </row>
-    <row r="73" spans="2:53" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:53" x14ac:dyDescent="0.2">
       <c r="E73" s="165"/>
       <c r="H73" s="166"/>
       <c r="L73" s="343">
@@ -12554,7 +12554,7 @@
       <c r="AW73" s="25"/>
       <c r="AX73" s="25"/>
     </row>
-    <row r="74" spans="2:53" ht="11.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:53" ht="10.8" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E74" s="165"/>
       <c r="H74" s="166"/>
       <c r="L74" s="308">
@@ -12611,7 +12611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:53" ht="11.25" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:53" ht="10.8" thickBot="1" x14ac:dyDescent="0.25">
       <c r="E75" s="165"/>
       <c r="H75" s="166"/>
       <c r="L75" s="344">
@@ -12677,7 +12677,7 @@
         <v>2145014465.875</v>
       </c>
     </row>
-    <row r="76" spans="2:53" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:53" x14ac:dyDescent="0.2">
       <c r="C76" s="173" t="s">
         <v>25</v>
       </c>
@@ -12715,7 +12715,7 @@
       <c r="AW76" s="25"/>
       <c r="AX76" s="25"/>
     </row>
-    <row r="77" spans="2:53" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:53" x14ac:dyDescent="0.2">
       <c r="E77" s="165"/>
       <c r="H77" s="166"/>
       <c r="P77" s="167"/>
@@ -12750,7 +12750,7 @@
       <c r="AW77" s="25"/>
       <c r="AX77" s="25"/>
     </row>
-    <row r="78" spans="2:53" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:53" x14ac:dyDescent="0.2">
       <c r="C78" s="172" t="s">
         <v>46</v>
       </c>
@@ -12794,7 +12794,7 @@
       <c r="AW78" s="25"/>
       <c r="AX78" s="25"/>
     </row>
-    <row r="79" spans="2:53" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:53" x14ac:dyDescent="0.2">
       <c r="C79" s="172" t="s">
         <v>66</v>
       </c>
@@ -12838,7 +12838,7 @@
       <c r="AW79" s="25"/>
       <c r="AX79" s="25"/>
     </row>
-    <row r="80" spans="2:53" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:53" x14ac:dyDescent="0.2">
       <c r="C80" s="172"/>
       <c r="D80"/>
       <c r="G80" s="172"/>
@@ -12880,7 +12880,7 @@
       <c r="AW80" s="25"/>
       <c r="AX80" s="25"/>
     </row>
-    <row r="81" spans="2:50" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:50" x14ac:dyDescent="0.2">
       <c r="C81" s="172" t="s">
         <v>67</v>
       </c>
@@ -12924,7 +12924,7 @@
       <c r="AW81" s="25"/>
       <c r="AX81" s="25"/>
     </row>
-    <row r="82" spans="2:50" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:50" x14ac:dyDescent="0.2">
       <c r="C82" s="172" t="s">
         <v>68</v>
       </c>
@@ -12967,7 +12967,7 @@
       <c r="AW82" s="25"/>
       <c r="AX82" s="25"/>
     </row>
-    <row r="83" spans="2:50" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:50" x14ac:dyDescent="0.2">
       <c r="C83" s="24"/>
       <c r="D83"/>
       <c r="G83" s="172"/>
@@ -13008,7 +13008,7 @@
       <c r="AW83" s="25"/>
       <c r="AX83" s="25"/>
     </row>
-    <row r="84" spans="2:50" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:50" x14ac:dyDescent="0.2">
       <c r="B84" s="6"/>
       <c r="C84" s="172" t="s">
         <v>69</v>
@@ -13052,7 +13052,7 @@
       <c r="AW84" s="25"/>
       <c r="AX84" s="25"/>
     </row>
-    <row r="85" spans="2:50" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:50" x14ac:dyDescent="0.2">
       <c r="C85" s="172"/>
       <c r="D85" s="24"/>
       <c r="G85" s="172"/>
@@ -13090,7 +13090,7 @@
       <c r="AW85" s="25"/>
       <c r="AX85" s="25"/>
     </row>
-    <row r="86" spans="2:50" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:50" x14ac:dyDescent="0.2">
       <c r="C86" s="172"/>
       <c r="D86" s="24"/>
       <c r="G86" s="172"/>
@@ -13128,7 +13128,7 @@
       <c r="AW86" s="25"/>
       <c r="AX86" s="25"/>
     </row>
-    <row r="87" spans="2:50" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:50" x14ac:dyDescent="0.2">
       <c r="B87" s="10" t="s">
         <v>70</v>
       </c>
@@ -13169,7 +13169,7 @@
       <c r="AW87" s="25"/>
       <c r="AX87" s="25"/>
     </row>
-    <row r="88" spans="2:50" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:50" x14ac:dyDescent="0.2">
       <c r="C88" s="172"/>
       <c r="D88" s="24"/>
       <c r="F88" s="172"/>
@@ -13207,7 +13207,7 @@
       <c r="AW88" s="25"/>
       <c r="AX88" s="25"/>
     </row>
-    <row r="89" spans="2:50" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:50" x14ac:dyDescent="0.2">
       <c r="C89" s="24">
         <v>1</v>
       </c>
@@ -13231,7 +13231,7 @@
       <c r="N89"/>
       <c r="O89"/>
     </row>
-    <row r="90" spans="2:50" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:50" x14ac:dyDescent="0.2">
       <c r="C90"/>
       <c r="D90" s="24" t="s">
         <v>73</v>
@@ -13252,7 +13252,7 @@
       <c r="N90"/>
       <c r="O90"/>
     </row>
-    <row r="91" spans="2:50" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:50" x14ac:dyDescent="0.2">
       <c r="C91"/>
       <c r="D91" s="24" t="s">
         <v>20</v>
@@ -13272,7 +13272,7 @@
       <c r="N91"/>
       <c r="O91"/>
     </row>
-    <row r="92" spans="2:50" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:50" x14ac:dyDescent="0.2">
       <c r="C92"/>
       <c r="D92"/>
       <c r="E92" s="13" t="s">
@@ -13287,7 +13287,7 @@
       <c r="N92"/>
       <c r="O92"/>
     </row>
-    <row r="93" spans="2:50" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:50" x14ac:dyDescent="0.2">
       <c r="C93"/>
       <c r="D93"/>
       <c r="H93"/>
@@ -13299,7 +13299,7 @@
       <c r="N93"/>
       <c r="O93"/>
     </row>
-    <row r="94" spans="2:50" x14ac:dyDescent="0.15">
+    <row r="94" spans="2:50" x14ac:dyDescent="0.2">
       <c r="C94"/>
       <c r="D94"/>
       <c r="H94"/>
@@ -13311,7 +13311,7 @@
       <c r="N94"/>
       <c r="O94"/>
     </row>
-    <row r="95" spans="2:50" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:50" x14ac:dyDescent="0.2">
       <c r="C95"/>
       <c r="D95"/>
       <c r="H95"/>
@@ -13323,7 +13323,7 @@
       <c r="N95"/>
       <c r="O95"/>
     </row>
-    <row r="96" spans="2:50" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:50" x14ac:dyDescent="0.2">
       <c r="C96"/>
       <c r="D96"/>
       <c r="H96"/>
@@ -13335,7 +13335,7 @@
       <c r="N96"/>
       <c r="O96"/>
     </row>
-    <row r="97" spans="3:15" x14ac:dyDescent="0.15">
+    <row r="97" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C97"/>
       <c r="D97"/>
       <c r="H97"/>
@@ -13347,7 +13347,7 @@
       <c r="N97"/>
       <c r="O97"/>
     </row>
-    <row r="98" spans="3:15" x14ac:dyDescent="0.15">
+    <row r="98" spans="3:15" x14ac:dyDescent="0.2">
       <c r="C98"/>
       <c r="D98"/>
       <c r="H98"/>
@@ -13361,26 +13361,16 @@
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="AP6:AS6"/>
-    <mergeCell ref="AP7:AP8"/>
-    <mergeCell ref="AQ7:AQ8"/>
-    <mergeCell ref="AR7:AR8"/>
-    <mergeCell ref="AS7:AS8"/>
-    <mergeCell ref="AK7:AK8"/>
-    <mergeCell ref="AL7:AL8"/>
-    <mergeCell ref="AM7:AM8"/>
-    <mergeCell ref="AK6:AN6"/>
-    <mergeCell ref="AN7:AN8"/>
-    <mergeCell ref="AA6:AD6"/>
-    <mergeCell ref="AA7:AA8"/>
-    <mergeCell ref="AB7:AB8"/>
-    <mergeCell ref="AC7:AC8"/>
-    <mergeCell ref="AD7:AD8"/>
-    <mergeCell ref="T7:T8"/>
-    <mergeCell ref="U7:U8"/>
-    <mergeCell ref="V7:V8"/>
-    <mergeCell ref="W7:W8"/>
-    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="AU6:AX6"/>
+    <mergeCell ref="AU7:AU8"/>
+    <mergeCell ref="AV7:AV8"/>
+    <mergeCell ref="AW7:AW8"/>
+    <mergeCell ref="AX7:AX8"/>
+    <mergeCell ref="AF6:AI6"/>
+    <mergeCell ref="AF7:AF8"/>
+    <mergeCell ref="AG7:AG8"/>
+    <mergeCell ref="AH7:AH8"/>
+    <mergeCell ref="AI7:AI8"/>
     <mergeCell ref="X6:Y7"/>
     <mergeCell ref="B6:B8"/>
     <mergeCell ref="C6:C8"/>
@@ -13397,16 +13387,26 @@
     <mergeCell ref="P6:S6"/>
     <mergeCell ref="R7:S7"/>
     <mergeCell ref="T6:U6"/>
-    <mergeCell ref="AF6:AI6"/>
-    <mergeCell ref="AF7:AF8"/>
-    <mergeCell ref="AG7:AG8"/>
-    <mergeCell ref="AH7:AH8"/>
-    <mergeCell ref="AI7:AI8"/>
-    <mergeCell ref="AU6:AX6"/>
-    <mergeCell ref="AU7:AU8"/>
-    <mergeCell ref="AV7:AV8"/>
-    <mergeCell ref="AW7:AW8"/>
-    <mergeCell ref="AX7:AX8"/>
+    <mergeCell ref="T7:T8"/>
+    <mergeCell ref="U7:U8"/>
+    <mergeCell ref="V7:V8"/>
+    <mergeCell ref="W7:W8"/>
+    <mergeCell ref="V6:W6"/>
+    <mergeCell ref="AA6:AD6"/>
+    <mergeCell ref="AA7:AA8"/>
+    <mergeCell ref="AB7:AB8"/>
+    <mergeCell ref="AC7:AC8"/>
+    <mergeCell ref="AD7:AD8"/>
+    <mergeCell ref="AK7:AK8"/>
+    <mergeCell ref="AL7:AL8"/>
+    <mergeCell ref="AM7:AM8"/>
+    <mergeCell ref="AK6:AN6"/>
+    <mergeCell ref="AN7:AN8"/>
+    <mergeCell ref="AP6:AS6"/>
+    <mergeCell ref="AP7:AP8"/>
+    <mergeCell ref="AQ7:AQ8"/>
+    <mergeCell ref="AR7:AR8"/>
+    <mergeCell ref="AS7:AS8"/>
   </mergeCells>
   <pageMargins left="1.6929133858267718" right="0" top="1.1417322834645669" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13419,52 +13419,52 @@
     <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="B1:BK84"/>
-  <sheetFormatPr defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="179" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" style="23" customWidth="1"/>
-    <col min="5" max="5" width="2.83203125" customWidth="1"/>
-    <col min="6" max="6" width="35.1640625" customWidth="1"/>
+    <col min="1" max="1" width="2.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="179" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="23" customWidth="1"/>
+    <col min="5" max="5" width="2.85546875" customWidth="1"/>
+    <col min="6" max="6" width="35.140625" customWidth="1"/>
     <col min="7" max="7" width="14" style="24" customWidth="1"/>
-    <col min="8" max="8" width="17.5" style="25" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" style="25" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" style="25" hidden="1" customWidth="1"/>
-    <col min="11" max="13" width="18.5" style="25" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="18.5" style="25" customWidth="1"/>
-    <col min="15" max="15" width="5.5" style="25" customWidth="1"/>
-    <col min="16" max="16" width="7.1640625" style="25" customWidth="1"/>
-    <col min="17" max="18" width="7.83203125" customWidth="1"/>
-    <col min="19" max="19" width="8.33203125" customWidth="1"/>
-    <col min="20" max="22" width="7.83203125" customWidth="1"/>
-    <col min="23" max="23" width="12.1640625" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" style="25" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" style="25" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" style="25" hidden="1" customWidth="1"/>
+    <col min="11" max="13" width="18.42578125" style="25" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="18.42578125" style="25" customWidth="1"/>
+    <col min="15" max="15" width="5.42578125" style="25" customWidth="1"/>
+    <col min="16" max="16" width="7.140625" style="25" customWidth="1"/>
+    <col min="17" max="18" width="7.85546875" customWidth="1"/>
+    <col min="19" max="19" width="8.28515625" customWidth="1"/>
+    <col min="20" max="22" width="7.85546875" customWidth="1"/>
+    <col min="23" max="23" width="12.140625" customWidth="1"/>
     <col min="24" max="24" width="15" customWidth="1"/>
-    <col min="25" max="25" width="6.5" customWidth="1"/>
-    <col min="26" max="26" width="6.83203125" customWidth="1"/>
-    <col min="27" max="27" width="13.83203125" customWidth="1"/>
-    <col min="28" max="28" width="16.6640625" customWidth="1"/>
-    <col min="29" max="29" width="14.5" customWidth="1"/>
+    <col min="25" max="25" width="6.42578125" customWidth="1"/>
+    <col min="26" max="26" width="6.85546875" customWidth="1"/>
+    <col min="27" max="27" width="13.85546875" customWidth="1"/>
+    <col min="28" max="28" width="16.7109375" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" customWidth="1"/>
     <col min="30" max="30" width="8" customWidth="1"/>
-    <col min="31" max="31" width="8.1640625" customWidth="1"/>
-    <col min="32" max="32" width="13.83203125" customWidth="1"/>
-    <col min="33" max="34" width="16.1640625" customWidth="1"/>
-    <col min="35" max="35" width="7.83203125" customWidth="1"/>
-    <col min="36" max="36" width="9.5" customWidth="1"/>
-    <col min="37" max="39" width="16.1640625" customWidth="1"/>
-    <col min="40" max="40" width="10.6640625" customWidth="1"/>
-    <col min="41" max="41" width="10.83203125" customWidth="1"/>
-    <col min="42" max="43" width="16.1640625" customWidth="1"/>
-    <col min="44" max="44" width="17.6640625" customWidth="1"/>
-    <col min="45" max="45" width="9.33203125" customWidth="1"/>
-    <col min="46" max="46" width="8.6640625" customWidth="1"/>
-    <col min="47" max="49" width="17.6640625" customWidth="1"/>
-    <col min="50" max="50" width="1.1640625" customWidth="1"/>
+    <col min="31" max="31" width="8.140625" customWidth="1"/>
+    <col min="32" max="32" width="13.85546875" customWidth="1"/>
+    <col min="33" max="34" width="16.140625" customWidth="1"/>
+    <col min="35" max="35" width="7.85546875" customWidth="1"/>
+    <col min="36" max="36" width="9.42578125" customWidth="1"/>
+    <col min="37" max="39" width="16.140625" customWidth="1"/>
+    <col min="40" max="40" width="10.7109375" customWidth="1"/>
+    <col min="41" max="41" width="10.85546875" customWidth="1"/>
+    <col min="42" max="43" width="16.140625" customWidth="1"/>
+    <col min="44" max="44" width="17.7109375" customWidth="1"/>
+    <col min="45" max="45" width="9.28515625" customWidth="1"/>
+    <col min="46" max="46" width="8.7109375" customWidth="1"/>
+    <col min="47" max="49" width="17.7109375" customWidth="1"/>
+    <col min="50" max="50" width="1.140625" customWidth="1"/>
     <col min="51" max="51" width="14" customWidth="1"/>
-    <col min="52" max="63" width="12.83203125" customWidth="1"/>
+    <col min="52" max="63" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:63" ht="11.25" thickBot="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:63" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:63" ht="10.8" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:63" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="14" t="s">
         <v>22</v>
       </c>
@@ -13521,7 +13521,7 @@
       <c r="AV2" s="2"/>
       <c r="AW2" s="2"/>
     </row>
-    <row r="3" spans="2:63" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:63" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>23</v>
       </c>
@@ -13577,7 +13577,7 @@
       <c r="AV3" s="34"/>
       <c r="AW3" s="34"/>
     </row>
-    <row r="4" spans="2:63" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:63" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -13633,7 +13633,7 @@
       <c r="AV4" s="2"/>
       <c r="AW4" s="2"/>
     </row>
-    <row r="6" spans="2:63" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:63" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="391" t="s">
         <v>7</v>
       </c>
@@ -13641,42 +13641,42 @@
         <v>29</v>
       </c>
       <c r="D6" s="41"/>
-      <c r="E6" s="399" t="s">
+      <c r="E6" s="403" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="400"/>
+      <c r="F6" s="404"/>
       <c r="G6" s="431" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="409" t="s">
+      <c r="H6" s="413" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="409"/>
-      <c r="J6" s="409"/>
-      <c r="K6" s="409"/>
-      <c r="L6" s="414" t="s">
+      <c r="I6" s="413"/>
+      <c r="J6" s="413"/>
+      <c r="K6" s="413"/>
+      <c r="L6" s="418" t="s">
         <v>32</v>
       </c>
-      <c r="M6" s="415"/>
-      <c r="N6" s="416"/>
-      <c r="O6" s="417" t="s">
+      <c r="M6" s="419"/>
+      <c r="N6" s="420"/>
+      <c r="O6" s="421" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="418"/>
-      <c r="Q6" s="418"/>
-      <c r="R6" s="419"/>
-      <c r="S6" s="420" t="s">
+      <c r="P6" s="422"/>
+      <c r="Q6" s="422"/>
+      <c r="R6" s="423"/>
+      <c r="S6" s="396" t="s">
         <v>34</v>
       </c>
-      <c r="T6" s="421"/>
-      <c r="U6" s="420" t="s">
+      <c r="T6" s="397"/>
+      <c r="U6" s="396" t="s">
         <v>35</v>
       </c>
-      <c r="V6" s="421"/>
-      <c r="W6" s="394" t="s">
+      <c r="V6" s="397"/>
+      <c r="W6" s="398" t="s">
         <v>36</v>
       </c>
-      <c r="X6" s="395"/>
+      <c r="X6" s="399"/>
       <c r="Y6" s="424">
         <v>44926</v>
       </c>
@@ -13713,60 +13713,60 @@
       <c r="AV6" s="425"/>
       <c r="AW6" s="426"/>
     </row>
-    <row r="7" spans="2:63" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:63" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="391"/>
       <c r="C7" s="430"/>
       <c r="D7" s="43" t="s">
         <v>76</v>
       </c>
-      <c r="E7" s="401"/>
-      <c r="F7" s="402"/>
+      <c r="E7" s="405"/>
+      <c r="F7" s="406"/>
       <c r="G7" s="432"/>
-      <c r="H7" s="410">
+      <c r="H7" s="414">
         <v>43100</v>
       </c>
-      <c r="I7" s="411" t="s">
+      <c r="I7" s="415" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="411" t="s">
+      <c r="J7" s="415" t="s">
         <v>39</v>
       </c>
       <c r="K7" s="44">
         <v>43465</v>
       </c>
-      <c r="L7" s="411" t="s">
+      <c r="L7" s="415" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="411" t="s">
+      <c r="M7" s="415" t="s">
         <v>9</v>
       </c>
       <c r="N7" s="44">
         <f>K7</f>
         <v>43465</v>
       </c>
-      <c r="O7" s="412" t="s">
+      <c r="O7" s="416" t="s">
         <v>40</v>
       </c>
-      <c r="P7" s="413"/>
-      <c r="Q7" s="412" t="s">
+      <c r="P7" s="417"/>
+      <c r="Q7" s="416" t="s">
         <v>41</v>
       </c>
-      <c r="R7" s="413"/>
-      <c r="S7" s="422" t="s">
+      <c r="R7" s="417"/>
+      <c r="S7" s="394" t="s">
         <v>42</v>
       </c>
-      <c r="T7" s="422" t="s">
+      <c r="T7" s="394" t="s">
         <v>43</v>
       </c>
-      <c r="U7" s="422" t="s">
+      <c r="U7" s="394" t="s">
         <v>42</v>
       </c>
-      <c r="V7" s="422" t="s">
+      <c r="V7" s="394" t="s">
         <v>43</v>
       </c>
-      <c r="W7" s="396"/>
-      <c r="X7" s="397"/>
-      <c r="Y7" s="405" t="s">
+      <c r="W7" s="400"/>
+      <c r="X7" s="401"/>
+      <c r="Y7" s="409" t="s">
         <v>44</v>
       </c>
       <c r="Z7" s="427"/>
@@ -13779,7 +13779,7 @@
       <c r="AC7" s="392" t="s">
         <v>26</v>
       </c>
-      <c r="AD7" s="405" t="s">
+      <c r="AD7" s="409" t="s">
         <v>44</v>
       </c>
       <c r="AE7" s="427"/>
@@ -13792,7 +13792,7 @@
       <c r="AH7" s="392" t="s">
         <v>26</v>
       </c>
-      <c r="AI7" s="405" t="s">
+      <c r="AI7" s="409" t="s">
         <v>44</v>
       </c>
       <c r="AJ7" s="427"/>
@@ -13805,7 +13805,7 @@
       <c r="AM7" s="392" t="s">
         <v>26</v>
       </c>
-      <c r="AN7" s="405" t="s">
+      <c r="AN7" s="409" t="s">
         <v>44</v>
       </c>
       <c r="AO7" s="427"/>
@@ -13818,7 +13818,7 @@
       <c r="AR7" s="392" t="s">
         <v>26</v>
       </c>
-      <c r="AS7" s="405" t="s">
+      <c r="AS7" s="409" t="s">
         <v>44</v>
       </c>
       <c r="AT7" s="427"/>
@@ -13871,21 +13871,21 @@
         <v>271</v>
       </c>
     </row>
-    <row r="8" spans="2:63" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:63" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="391"/>
       <c r="C8" s="430"/>
       <c r="D8" s="45"/>
-      <c r="E8" s="403"/>
-      <c r="F8" s="404"/>
+      <c r="E8" s="407"/>
+      <c r="F8" s="408"/>
       <c r="G8" s="433"/>
-      <c r="H8" s="411"/>
-      <c r="I8" s="411"/>
-      <c r="J8" s="411"/>
+      <c r="H8" s="415"/>
+      <c r="I8" s="415"/>
+      <c r="J8" s="415"/>
       <c r="K8" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="411"/>
-      <c r="M8" s="411"/>
+      <c r="L8" s="415"/>
+      <c r="M8" s="415"/>
       <c r="N8" s="48" t="s">
         <v>11</v>
       </c>
@@ -13901,10 +13901,10 @@
       <c r="R8" s="49" t="s">
         <v>42</v>
       </c>
-      <c r="S8" s="423"/>
-      <c r="T8" s="423"/>
-      <c r="U8" s="423"/>
-      <c r="V8" s="423"/>
+      <c r="S8" s="395"/>
+      <c r="T8" s="395"/>
+      <c r="U8" s="395"/>
+      <c r="V8" s="395"/>
       <c r="W8" s="50" t="s">
         <v>40</v>
       </c>
@@ -13952,7 +13952,7 @@
       <c r="BJ8" s="199"/>
       <c r="BK8" s="199"/>
     </row>
-    <row r="9" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B9" s="52"/>
       <c r="C9" s="183"/>
       <c r="D9" s="54"/>
@@ -14002,7 +14002,7 @@
       <c r="AV9" s="52"/>
       <c r="AW9" s="52"/>
     </row>
-    <row r="10" spans="2:63" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:63" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B10" s="61"/>
       <c r="C10" s="184" t="s">
         <v>6</v>
@@ -14067,7 +14067,7 @@
       <c r="BJ10" s="208"/>
       <c r="BK10" s="208"/>
     </row>
-    <row r="11" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B11" s="68"/>
       <c r="C11" s="89"/>
       <c r="D11" s="70"/>
@@ -14117,7 +14117,7 @@
       <c r="AV11" s="68"/>
       <c r="AW11" s="68"/>
     </row>
-    <row r="12" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B12" s="75"/>
       <c r="C12" s="76">
         <v>41722</v>
@@ -14329,7 +14329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B13" s="75"/>
       <c r="C13" s="76">
         <v>41750</v>
@@ -14541,7 +14541,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B14" s="75"/>
       <c r="C14" s="76">
         <v>41817</v>
@@ -14753,7 +14753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B15" s="75"/>
       <c r="C15" s="76">
         <v>41817</v>
@@ -14965,7 +14965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B16" s="75"/>
       <c r="C16" s="76">
         <v>41926</v>
@@ -15177,7 +15177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B17" s="75"/>
       <c r="C17" s="76">
         <v>41934</v>
@@ -15389,7 +15389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B18" s="75"/>
       <c r="C18" s="76">
         <v>42010</v>
@@ -15601,7 +15601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B19" s="75"/>
       <c r="C19" s="76">
         <v>42033</v>
@@ -15813,7 +15813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B20" s="75"/>
       <c r="C20" s="76">
         <v>42102</v>
@@ -16025,7 +16025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B21" s="75"/>
       <c r="C21" s="76">
         <v>42107</v>
@@ -16237,7 +16237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B22" s="75"/>
       <c r="C22" s="76">
         <v>42116</v>
@@ -16449,7 +16449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B23" s="75"/>
       <c r="C23" s="76">
         <v>42137</v>
@@ -16661,7 +16661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B24" s="75"/>
       <c r="C24" s="76">
         <v>42247</v>
@@ -16873,7 +16873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B25" s="75"/>
       <c r="C25" s="76">
         <v>42325</v>
@@ -17085,7 +17085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B26" s="75"/>
       <c r="C26" s="76">
         <v>42380</v>
@@ -17297,7 +17297,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B27" s="75"/>
       <c r="C27" s="76">
         <v>42411</v>
@@ -17509,7 +17509,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B28" s="75"/>
       <c r="C28" s="76">
         <v>42426</v>
@@ -17721,7 +17721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B29" s="75"/>
       <c r="C29" s="76">
         <v>42440</v>
@@ -17933,7 +17933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B30" s="75"/>
       <c r="C30" s="76">
         <v>42487</v>
@@ -18145,7 +18145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B31" s="75"/>
       <c r="C31" s="76">
         <v>42523</v>
@@ -18357,7 +18357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B32" s="75"/>
       <c r="C32" s="76">
         <v>42543</v>
@@ -18569,7 +18569,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B33" s="75"/>
       <c r="C33" s="76">
         <v>42545</v>
@@ -18781,7 +18781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B34" s="75"/>
       <c r="C34" s="76">
         <v>42552</v>
@@ -18993,7 +18993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B35" s="75"/>
       <c r="C35" s="76">
         <v>42552</v>
@@ -19205,7 +19205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B36" s="75"/>
       <c r="C36" s="76">
         <v>42653</v>
@@ -19417,7 +19417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B37" s="75"/>
       <c r="C37" s="76">
         <v>42650</v>
@@ -19629,7 +19629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B38" s="75"/>
       <c r="C38" s="76">
         <v>42650</v>
@@ -19841,7 +19841,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B39" s="75"/>
       <c r="C39" s="76">
         <v>42670</v>
@@ -20053,7 +20053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B40" s="75"/>
       <c r="C40" s="76">
         <v>42685</v>
@@ -20265,7 +20265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B41" s="68"/>
       <c r="C41" s="89"/>
       <c r="D41" s="70"/>
@@ -20316,7 +20316,7 @@
       <c r="AW41" s="96"/>
       <c r="AY41" s="196"/>
     </row>
-    <row r="42" spans="2:63" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:63" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B42" s="97"/>
       <c r="C42" s="98">
         <v>43158</v>
@@ -20523,7 +20523,7 @@
         <v>470000</v>
       </c>
     </row>
-    <row r="43" spans="2:63" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:63" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B43" s="97"/>
       <c r="C43" s="98">
         <v>43193</v>
@@ -20730,7 +20730,7 @@
         <v>166666.66666666666</v>
       </c>
     </row>
-    <row r="44" spans="2:63" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:63" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B44" s="97"/>
       <c r="C44" s="98">
         <v>43202</v>
@@ -20937,7 +20937,7 @@
         <v>83333.333333333328</v>
       </c>
     </row>
-    <row r="45" spans="2:63" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:63" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B45" s="97"/>
       <c r="C45" s="98">
         <v>43202</v>
@@ -21144,7 +21144,7 @@
         <v>83333.333333333328</v>
       </c>
     </row>
-    <row r="46" spans="2:63" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:63" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B46" s="97"/>
       <c r="C46" s="98">
         <v>43214</v>
@@ -21351,7 +21351,7 @@
         <v>166666.66666666666</v>
       </c>
     </row>
-    <row r="47" spans="2:63" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:63" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B47" s="97"/>
       <c r="C47" s="98">
         <v>43224</v>
@@ -21558,7 +21558,7 @@
         <v>117208.33333333333</v>
       </c>
     </row>
-    <row r="48" spans="2:63" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:63" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B48" s="209"/>
       <c r="C48" s="98"/>
       <c r="D48" s="99"/>
@@ -21621,7 +21621,7 @@
       <c r="BJ48" s="172"/>
       <c r="BK48" s="172"/>
     </row>
-    <row r="49" spans="2:63" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:63" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B49" s="209"/>
       <c r="C49" s="98">
         <v>43487</v>
@@ -21822,7 +21822,7 @@
         <v>145833.33333333334</v>
       </c>
     </row>
-    <row r="50" spans="2:63" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:63" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B50" s="209"/>
       <c r="C50" s="98">
         <v>43496</v>
@@ -22023,7 +22023,7 @@
         <v>203333.33333333334</v>
       </c>
     </row>
-    <row r="51" spans="2:63" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:63" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B51" s="209"/>
       <c r="C51" s="210"/>
       <c r="D51" s="211"/>
@@ -22086,7 +22086,7 @@
       <c r="BJ51" s="172"/>
       <c r="BK51" s="172"/>
     </row>
-    <row r="52" spans="2:63" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:63" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B52" s="209"/>
       <c r="C52" s="328">
         <v>45474</v>
@@ -22260,7 +22260,7 @@
         <v>9862049.7166666668</v>
       </c>
     </row>
-    <row r="53" spans="2:63" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:63" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B53" s="209"/>
       <c r="C53" s="210"/>
       <c r="D53" s="211"/>
@@ -22323,7 +22323,7 @@
       <c r="BJ53" s="172"/>
       <c r="BK53" s="172"/>
     </row>
-    <row r="54" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B54" s="140"/>
       <c r="C54" s="141"/>
       <c r="D54" s="142"/>
@@ -22374,7 +22374,7 @@
       <c r="AW54" s="153"/>
       <c r="AY54" s="196"/>
     </row>
-    <row r="55" spans="2:63" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:63" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B55" s="9"/>
       <c r="C55" s="155"/>
       <c r="D55" s="156"/>
@@ -22533,7 +22533,7 @@
         <v>11298424.716666667</v>
       </c>
     </row>
-    <row r="56" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:63" x14ac:dyDescent="0.2">
       <c r="E56" s="165"/>
       <c r="G56" s="166"/>
       <c r="Q56" s="167"/>
@@ -22568,7 +22568,7 @@
       <c r="AV56" s="25"/>
       <c r="AW56" s="25"/>
     </row>
-    <row r="57" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:63" x14ac:dyDescent="0.2">
       <c r="E57" s="165"/>
       <c r="G57" s="166">
         <f>100/Q57/100</f>
@@ -22608,7 +22608,7 @@
       <c r="AV57" s="25"/>
       <c r="AW57" s="25"/>
     </row>
-    <row r="58" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B58" s="10" t="s">
         <v>65</v>
       </c>
@@ -22653,7 +22653,7 @@
       <c r="AV58" s="25"/>
       <c r="AW58" s="25"/>
     </row>
-    <row r="59" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:63" x14ac:dyDescent="0.2">
       <c r="B59" s="10"/>
       <c r="C59" s="23"/>
       <c r="E59" s="165"/>
@@ -22696,7 +22696,7 @@
       <c r="AV59" s="25"/>
       <c r="AW59" s="25"/>
     </row>
-    <row r="60" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:63" x14ac:dyDescent="0.2">
       <c r="C60" s="173" t="s">
         <v>12</v>
       </c>
@@ -22735,7 +22735,7 @@
       <c r="AV60" s="25"/>
       <c r="AW60" s="25"/>
     </row>
-    <row r="61" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:63" x14ac:dyDescent="0.2">
       <c r="C61" s="172" t="s">
         <v>46</v>
       </c>
@@ -22781,7 +22781,7 @@
       <c r="AV61" s="25"/>
       <c r="AW61" s="25"/>
     </row>
-    <row r="62" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:63" x14ac:dyDescent="0.2">
       <c r="C62" s="172" t="s">
         <v>66</v>
       </c>
@@ -22827,7 +22827,7 @@
       <c r="AV62" s="25"/>
       <c r="AW62" s="25"/>
     </row>
-    <row r="63" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:63" x14ac:dyDescent="0.2">
       <c r="C63" s="172"/>
       <c r="E63" s="165"/>
       <c r="G63"/>
@@ -22871,7 +22871,7 @@
       <c r="AV63" s="25"/>
       <c r="AW63" s="25"/>
     </row>
-    <row r="64" spans="2:63" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:63" x14ac:dyDescent="0.2">
       <c r="C64" s="23"/>
       <c r="E64" s="165"/>
       <c r="G64"/>
@@ -22888,7 +22888,7 @@
       <c r="O64"/>
       <c r="P64"/>
     </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="23"/>
       <c r="E65" s="165"/>
       <c r="G65"/>
@@ -22905,7 +22905,7 @@
       <c r="O65"/>
       <c r="P65"/>
     </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="173" t="s">
         <v>25</v>
       </c>
@@ -22923,7 +22923,7 @@
       <c r="O66"/>
       <c r="P66"/>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="23"/>
       <c r="E67" s="165"/>
       <c r="G67"/>
@@ -22940,7 +22940,7 @@
       <c r="O67"/>
       <c r="P67"/>
     </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="172" t="s">
         <v>46</v>
       </c>
@@ -22959,7 +22959,7 @@
       <c r="O68"/>
       <c r="P68"/>
     </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="172" t="s">
         <v>66</v>
       </c>
@@ -22978,7 +22978,7 @@
       <c r="O69"/>
       <c r="P69"/>
     </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="172"/>
       <c r="D70"/>
       <c r="G70" s="172"/>
@@ -22995,7 +22995,7 @@
       <c r="O70"/>
       <c r="P70"/>
     </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="172" t="s">
         <v>67</v>
       </c>
@@ -23014,7 +23014,7 @@
       <c r="O71"/>
       <c r="P71"/>
     </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="172" t="s">
         <v>68</v>
       </c>
@@ -23033,7 +23033,7 @@
       <c r="O72"/>
       <c r="P72"/>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="24"/>
       <c r="D73"/>
       <c r="G73" s="172"/>
@@ -23050,7 +23050,7 @@
       <c r="O73"/>
       <c r="P73"/>
     </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B74" s="6"/>
       <c r="C74" s="172" t="s">
         <v>69</v>
@@ -23062,7 +23062,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B77" s="10" t="s">
         <v>70</v>
       </c>
@@ -23070,12 +23070,12 @@
       <c r="D77" s="24"/>
       <c r="F77" s="172"/>
     </row>
-    <row r="78" spans="2:16" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C78" s="172"/>
       <c r="D78" s="24"/>
       <c r="F78" s="172"/>
     </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C79" s="24">
         <v>1</v>
       </c>
@@ -23090,7 +23090,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80"/>
       <c r="D80" s="174" t="s">
         <v>71</v>
@@ -23104,7 +23104,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="81" spans="3:8" x14ac:dyDescent="0.15">
+    <row r="81" spans="3:8" x14ac:dyDescent="0.2">
       <c r="C81"/>
       <c r="D81" s="24" t="s">
         <v>73</v>
@@ -23118,28 +23118,48 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="82" spans="3:8" x14ac:dyDescent="0.15">
+    <row r="82" spans="3:8" x14ac:dyDescent="0.2">
       <c r="C82"/>
       <c r="D82"/>
       <c r="E82" s="13" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="83" spans="3:8" x14ac:dyDescent="0.15">
+    <row r="83" spans="3:8" x14ac:dyDescent="0.2">
       <c r="C83"/>
       <c r="D83"/>
     </row>
-    <row r="84" spans="3:8" x14ac:dyDescent="0.15">
+    <row r="84" spans="3:8" x14ac:dyDescent="0.2">
       <c r="C84"/>
       <c r="D84"/>
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="AN6:AR6"/>
-    <mergeCell ref="AN7:AO8"/>
-    <mergeCell ref="AP7:AP8"/>
-    <mergeCell ref="AQ7:AQ8"/>
-    <mergeCell ref="AR7:AR8"/>
+    <mergeCell ref="AS6:AW6"/>
+    <mergeCell ref="AS7:AT8"/>
+    <mergeCell ref="AU7:AU8"/>
+    <mergeCell ref="AV7:AV8"/>
+    <mergeCell ref="AW7:AW8"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="O6:R6"/>
+    <mergeCell ref="S6:T6"/>
+    <mergeCell ref="U6:V6"/>
+    <mergeCell ref="AD6:AH6"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="E6:F8"/>
+    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="W6:X7"/>
+    <mergeCell ref="Q7:R7"/>
+    <mergeCell ref="S7:S8"/>
+    <mergeCell ref="T7:T8"/>
+    <mergeCell ref="U7:U8"/>
+    <mergeCell ref="V7:V8"/>
     <mergeCell ref="L7:L8"/>
     <mergeCell ref="M7:M8"/>
     <mergeCell ref="AI6:AM6"/>
@@ -23156,31 +23176,11 @@
     <mergeCell ref="AF7:AF8"/>
     <mergeCell ref="AG7:AG8"/>
     <mergeCell ref="AH7:AH8"/>
-    <mergeCell ref="O7:P7"/>
-    <mergeCell ref="W6:X7"/>
-    <mergeCell ref="Q7:R7"/>
-    <mergeCell ref="S7:S8"/>
-    <mergeCell ref="T7:T8"/>
-    <mergeCell ref="U7:U8"/>
-    <mergeCell ref="V7:V8"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="E6:F8"/>
-    <mergeCell ref="G6:G8"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="O6:R6"/>
-    <mergeCell ref="S6:T6"/>
-    <mergeCell ref="U6:V6"/>
-    <mergeCell ref="AD6:AH6"/>
-    <mergeCell ref="AS6:AW6"/>
-    <mergeCell ref="AS7:AT8"/>
-    <mergeCell ref="AU7:AU8"/>
-    <mergeCell ref="AV7:AV8"/>
-    <mergeCell ref="AW7:AW8"/>
+    <mergeCell ref="AN6:AR6"/>
+    <mergeCell ref="AN7:AO8"/>
+    <mergeCell ref="AP7:AP8"/>
+    <mergeCell ref="AQ7:AQ8"/>
+    <mergeCell ref="AR7:AR8"/>
   </mergeCells>
   <pageMargins left="0.31496062992125984" right="0" top="0.94488188976377963" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="70" orientation="landscape" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -23190,23 +23190,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B1:O58"/>
-  <sheetFormatPr defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="179" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" style="23" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" customWidth="1"/>
-    <col min="6" max="6" width="35.1640625" customWidth="1"/>
+    <col min="1" max="1" width="2.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="179" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="23" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" customWidth="1"/>
+    <col min="6" max="6" width="35.140625" customWidth="1"/>
     <col min="7" max="7" width="14" style="24" customWidth="1"/>
-    <col min="8" max="8" width="17.5" style="25" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" style="25" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" style="25" customWidth="1"/>
-    <col min="11" max="14" width="18.5" style="25" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" style="25" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" style="25" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" style="25" customWidth="1"/>
+    <col min="11" max="14" width="18.42578125" style="25" customWidth="1"/>
     <col min="15" max="15" width="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:15" ht="11.25" thickBot="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:15" ht="10.8" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="14" t="s">
         <v>22</v>
       </c>
@@ -23235,7 +23235,7 @@
       </c>
       <c r="O2" s="434"/>
     </row>
-    <row r="3" spans="2:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:15" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>23</v>
       </c>
@@ -23259,7 +23259,7 @@
       <c r="N3" s="435"/>
       <c r="O3" s="435"/>
     </row>
-    <row r="4" spans="2:15" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:15" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -23283,7 +23283,7 @@
       <c r="N4" s="436"/>
       <c r="O4" s="436"/>
     </row>
-    <row r="6" spans="2:15" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:15" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="391" t="s">
         <v>7</v>
       </c>
@@ -23291,51 +23291,51 @@
         <v>29</v>
       </c>
       <c r="D6" s="41"/>
-      <c r="E6" s="399" t="s">
+      <c r="E6" s="403" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="400"/>
+      <c r="F6" s="404"/>
       <c r="G6" s="431" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="409" t="s">
+      <c r="H6" s="413" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="409"/>
-      <c r="J6" s="409"/>
-      <c r="K6" s="409"/>
-      <c r="L6" s="414" t="s">
+      <c r="I6" s="413"/>
+      <c r="J6" s="413"/>
+      <c r="K6" s="413"/>
+      <c r="L6" s="418" t="s">
         <v>32</v>
       </c>
-      <c r="M6" s="415"/>
-      <c r="N6" s="416"/>
+      <c r="M6" s="419"/>
+      <c r="N6" s="420"/>
       <c r="O6" s="42"/>
     </row>
-    <row r="7" spans="2:15" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:15" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="391"/>
       <c r="C7" s="430"/>
       <c r="D7" s="43" t="s">
         <v>37</v>
       </c>
-      <c r="E7" s="401"/>
-      <c r="F7" s="402"/>
+      <c r="E7" s="405"/>
+      <c r="F7" s="406"/>
       <c r="G7" s="432"/>
-      <c r="H7" s="410">
+      <c r="H7" s="414">
         <v>43100</v>
       </c>
-      <c r="I7" s="411" t="s">
+      <c r="I7" s="415" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="411" t="s">
+      <c r="J7" s="415" t="s">
         <v>39</v>
       </c>
       <c r="K7" s="44">
         <v>43465</v>
       </c>
-      <c r="L7" s="411" t="s">
+      <c r="L7" s="415" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="411" t="s">
+      <c r="M7" s="415" t="s">
         <v>9</v>
       </c>
       <c r="N7" s="44">
@@ -23344,27 +23344,27 @@
       </c>
       <c r="O7" s="42"/>
     </row>
-    <row r="8" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="391"/>
       <c r="C8" s="430"/>
       <c r="D8" s="45"/>
-      <c r="E8" s="403"/>
-      <c r="F8" s="404"/>
+      <c r="E8" s="407"/>
+      <c r="F8" s="408"/>
       <c r="G8" s="433"/>
-      <c r="H8" s="411"/>
-      <c r="I8" s="411"/>
-      <c r="J8" s="411"/>
+      <c r="H8" s="415"/>
+      <c r="I8" s="415"/>
+      <c r="J8" s="415"/>
       <c r="K8" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="411"/>
-      <c r="M8" s="411"/>
+      <c r="L8" s="415"/>
+      <c r="M8" s="415"/>
       <c r="N8" s="48" t="s">
         <v>11</v>
       </c>
       <c r="O8" s="42"/>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B9" s="52"/>
       <c r="C9" s="183"/>
       <c r="D9" s="54"/>
@@ -23380,7 +23380,7 @@
       <c r="N9" s="59"/>
       <c r="O9" s="60"/>
     </row>
-    <row r="10" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B10" s="61"/>
       <c r="C10" s="184" t="s">
         <v>13</v>
@@ -23398,7 +23398,7 @@
       <c r="N10" s="67"/>
       <c r="O10" s="42"/>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B11" s="68"/>
       <c r="C11" s="89"/>
       <c r="D11" s="70"/>
@@ -23414,7 +23414,7 @@
       <c r="N11" s="74"/>
       <c r="O11" s="60"/>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B12" s="68"/>
       <c r="C12" s="89"/>
       <c r="D12" s="70"/>
@@ -23432,7 +23432,7 @@
       <c r="N12" s="74"/>
       <c r="O12" s="60"/>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B13" s="68"/>
       <c r="C13" s="89"/>
       <c r="D13" s="70">
@@ -23460,7 +23460,7 @@
       </c>
       <c r="O13" s="60"/>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B14" s="68"/>
       <c r="C14" s="89"/>
       <c r="D14" s="70">
@@ -23488,7 +23488,7 @@
       </c>
       <c r="O14" s="60"/>
     </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B15" s="68"/>
       <c r="C15" s="89"/>
       <c r="D15" s="70">
@@ -23516,7 +23516,7 @@
       </c>
       <c r="O15" s="60"/>
     </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B16" s="68"/>
       <c r="C16" s="89"/>
       <c r="D16" s="70">
@@ -23544,7 +23544,7 @@
       </c>
       <c r="O16" s="60"/>
     </row>
-    <row r="17" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B17" s="68"/>
       <c r="C17" s="89"/>
       <c r="D17" s="70">
@@ -23572,7 +23572,7 @@
       </c>
       <c r="O17" s="60"/>
     </row>
-    <row r="18" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B18" s="68"/>
       <c r="C18" s="89"/>
       <c r="D18" s="70">
@@ -23600,7 +23600,7 @@
       </c>
       <c r="O18" s="60"/>
     </row>
-    <row r="19" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B19" s="140"/>
       <c r="C19" s="141"/>
       <c r="D19" s="142"/>
@@ -23616,7 +23616,7 @@
       <c r="N19" s="146"/>
       <c r="O19" s="60"/>
     </row>
-    <row r="20" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B20" s="140"/>
       <c r="C20" s="141"/>
       <c r="D20" s="142"/>
@@ -23641,7 +23641,7 @@
       </c>
       <c r="O20" s="60"/>
     </row>
-    <row r="21" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B21" s="140"/>
       <c r="C21" s="141"/>
       <c r="D21" s="142"/>
@@ -23657,7 +23657,7 @@
       <c r="N21" s="146"/>
       <c r="O21" s="60"/>
     </row>
-    <row r="22" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B22" s="140"/>
       <c r="C22" s="141"/>
       <c r="D22" s="70">
@@ -23679,7 +23679,7 @@
       </c>
       <c r="O22" s="60"/>
     </row>
-    <row r="23" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B23" s="140"/>
       <c r="C23" s="141"/>
       <c r="D23" s="70"/>
@@ -23695,7 +23695,7 @@
       <c r="N23" s="146"/>
       <c r="O23" s="60"/>
     </row>
-    <row r="24" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B24" s="140"/>
       <c r="C24" s="141"/>
       <c r="D24" s="142"/>
@@ -23714,7 +23714,7 @@
       </c>
       <c r="O24" s="60"/>
     </row>
-    <row r="25" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B25" s="140"/>
       <c r="C25" s="141"/>
       <c r="D25" s="142"/>
@@ -23730,7 +23730,7 @@
       <c r="N25" s="305"/>
       <c r="O25" s="60"/>
     </row>
-    <row r="26" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B26" s="140"/>
       <c r="C26" s="141"/>
       <c r="D26" s="70">
@@ -23752,7 +23752,7 @@
       </c>
       <c r="O26" s="60"/>
     </row>
-    <row r="27" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B27" s="140"/>
       <c r="C27" s="141"/>
       <c r="D27" s="70">
@@ -23774,7 +23774,7 @@
       </c>
       <c r="O27" s="60"/>
     </row>
-    <row r="28" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B28" s="140"/>
       <c r="C28" s="141"/>
       <c r="D28" s="70">
@@ -23796,7 +23796,7 @@
       </c>
       <c r="O28" s="60"/>
     </row>
-    <row r="29" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B29" s="140"/>
       <c r="C29" s="141"/>
       <c r="D29" s="70">
@@ -23818,7 +23818,7 @@
       </c>
       <c r="O29" s="60"/>
     </row>
-    <row r="30" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B30" s="140"/>
       <c r="C30" s="141"/>
       <c r="D30" s="142"/>
@@ -23834,7 +23834,7 @@
       <c r="N30" s="305"/>
       <c r="O30" s="60"/>
     </row>
-    <row r="31" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B31" s="140"/>
       <c r="C31" s="141"/>
       <c r="D31" s="142"/>
@@ -23853,7 +23853,7 @@
       </c>
       <c r="O31" s="60"/>
     </row>
-    <row r="32" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B32" s="140"/>
       <c r="C32" s="141"/>
       <c r="D32" s="142"/>
@@ -23869,7 +23869,7 @@
       <c r="N32" s="305"/>
       <c r="O32" s="60"/>
     </row>
-    <row r="33" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B33" s="140"/>
       <c r="C33" s="141"/>
       <c r="D33" s="142"/>
@@ -23885,7 +23885,7 @@
       <c r="N33" s="146"/>
       <c r="O33" s="60"/>
     </row>
-    <row r="34" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:15" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B34" s="9"/>
       <c r="C34" s="155"/>
       <c r="D34" s="156"/>
@@ -23904,33 +23904,33 @@
       </c>
       <c r="O34" s="9"/>
     </row>
-    <row r="35" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:15" x14ac:dyDescent="0.2">
       <c r="E35" s="165"/>
       <c r="G35" s="166"/>
     </row>
-    <row r="36" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:15" x14ac:dyDescent="0.2">
       <c r="E36" s="165"/>
       <c r="G36" s="166"/>
     </row>
-    <row r="37" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:15" x14ac:dyDescent="0.2">
       <c r="E37" s="165"/>
       <c r="G37" s="166"/>
     </row>
-    <row r="38" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:15" x14ac:dyDescent="0.2">
       <c r="E38" s="165"/>
       <c r="G38" s="166"/>
       <c r="H38" s="190"/>
       <c r="K38" s="176"/>
     </row>
-    <row r="39" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:15" x14ac:dyDescent="0.2">
       <c r="E39" s="165"/>
       <c r="G39" s="166"/>
     </row>
-    <row r="40" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:15" x14ac:dyDescent="0.2">
       <c r="E40" s="165"/>
       <c r="G40" s="166"/>
     </row>
-    <row r="41" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:15" x14ac:dyDescent="0.2">
       <c r="E41" s="165"/>
       <c r="G41" s="166"/>
       <c r="H41" s="191"/>
@@ -23938,35 +23938,35 @@
       <c r="K41" s="191"/>
       <c r="L41" s="191"/>
     </row>
-    <row r="42" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:15" x14ac:dyDescent="0.2">
       <c r="E42" s="165"/>
       <c r="G42" s="166"/>
     </row>
-    <row r="43" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:15" x14ac:dyDescent="0.2">
       <c r="E43" s="165"/>
       <c r="G43" s="166"/>
     </row>
-    <row r="44" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:15" x14ac:dyDescent="0.2">
       <c r="E44" s="165"/>
       <c r="G44" s="166"/>
     </row>
-    <row r="45" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:15" x14ac:dyDescent="0.2">
       <c r="E45" s="165"/>
       <c r="G45" s="166"/>
     </row>
-    <row r="46" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:15" x14ac:dyDescent="0.2">
       <c r="E46" s="165"/>
       <c r="G46" s="166"/>
     </row>
-    <row r="47" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:15" x14ac:dyDescent="0.2">
       <c r="E47" s="165"/>
       <c r="G47" s="166"/>
     </row>
-    <row r="48" spans="2:15" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:15" x14ac:dyDescent="0.2">
       <c r="E48" s="165"/>
       <c r="G48" s="166"/>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.15">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="192"/>
       <c r="D49"/>
       <c r="G49"/>
@@ -23978,7 +23978,7 @@
       <c r="M49"/>
       <c r="N49"/>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.15">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="192"/>
       <c r="D50"/>
       <c r="G50"/>
@@ -23990,7 +23990,7 @@
       <c r="M50"/>
       <c r="N50"/>
     </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.15">
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="192"/>
       <c r="D51"/>
       <c r="G51"/>
@@ -24002,7 +24002,7 @@
       <c r="M51"/>
       <c r="N51"/>
     </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.15">
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="192"/>
       <c r="D52"/>
       <c r="G52"/>
@@ -24014,7 +24014,7 @@
       <c r="M52"/>
       <c r="N52"/>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.15">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="192"/>
       <c r="D53"/>
       <c r="G53"/>
@@ -24026,7 +24026,7 @@
       <c r="M53"/>
       <c r="N53"/>
     </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.15">
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="192"/>
       <c r="D54"/>
       <c r="G54"/>
@@ -24038,7 +24038,7 @@
       <c r="M54"/>
       <c r="N54"/>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.15">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="192"/>
       <c r="D55"/>
       <c r="G55"/>
@@ -24050,7 +24050,7 @@
       <c r="M55"/>
       <c r="N55"/>
     </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.15">
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="192"/>
       <c r="D56"/>
       <c r="G56"/>
@@ -24062,7 +24062,7 @@
       <c r="M56"/>
       <c r="N56"/>
     </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.15">
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="192"/>
       <c r="D57"/>
       <c r="G57"/>
@@ -24074,7 +24074,7 @@
       <c r="M57"/>
       <c r="N57"/>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.15">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="192"/>
       <c r="D58"/>
       <c r="G58"/>
@@ -24109,45 +24109,45 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="B1:BH241"/>
-  <sheetFormatPr defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="23" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" style="23" customWidth="1"/>
-    <col min="5" max="5" width="2.83203125" customWidth="1"/>
-    <col min="6" max="6" width="35.1640625" customWidth="1"/>
+    <col min="1" max="1" width="2.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="23" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="23" customWidth="1"/>
+    <col min="5" max="5" width="2.85546875" customWidth="1"/>
+    <col min="6" max="6" width="35.140625" customWidth="1"/>
     <col min="7" max="7" width="14" style="24" customWidth="1"/>
-    <col min="8" max="8" width="17.5" style="25" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" style="25" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" style="25" hidden="1" customWidth="1"/>
-    <col min="11" max="13" width="18.5" style="25" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="18.5" style="25" customWidth="1"/>
-    <col min="15" max="16" width="7.83203125" customWidth="1"/>
-    <col min="17" max="17" width="8.33203125" customWidth="1"/>
-    <col min="18" max="20" width="7.83203125" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" style="25" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" style="25" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" style="25" hidden="1" customWidth="1"/>
+    <col min="11" max="13" width="18.42578125" style="25" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="18.42578125" style="25" customWidth="1"/>
+    <col min="15" max="16" width="7.85546875" customWidth="1"/>
+    <col min="17" max="17" width="8.28515625" customWidth="1"/>
+    <col min="18" max="20" width="7.85546875" customWidth="1"/>
     <col min="21" max="21" width="15" customWidth="1"/>
-    <col min="22" max="22" width="8.5" style="25" customWidth="1"/>
-    <col min="23" max="23" width="8.1640625" style="25" customWidth="1"/>
-    <col min="24" max="26" width="16.1640625" style="25" customWidth="1"/>
-    <col min="27" max="27" width="9.1640625" style="25" customWidth="1"/>
-    <col min="28" max="28" width="8.6640625" style="25" customWidth="1"/>
-    <col min="29" max="31" width="16.1640625" style="25" customWidth="1"/>
+    <col min="22" max="22" width="8.42578125" style="25" customWidth="1"/>
+    <col min="23" max="23" width="8.140625" style="25" customWidth="1"/>
+    <col min="24" max="26" width="16.140625" style="25" customWidth="1"/>
+    <col min="27" max="27" width="9.140625" style="25" customWidth="1"/>
+    <col min="28" max="28" width="8.7109375" style="25" customWidth="1"/>
+    <col min="29" max="31" width="16.140625" style="25" customWidth="1"/>
     <col min="32" max="32" width="10" style="25" customWidth="1"/>
-    <col min="33" max="33" width="10.6640625" style="25" customWidth="1"/>
-    <col min="34" max="36" width="16.1640625" style="25" customWidth="1"/>
+    <col min="33" max="33" width="10.7109375" style="25" customWidth="1"/>
+    <col min="34" max="36" width="16.140625" style="25" customWidth="1"/>
     <col min="37" max="37" width="10" style="25" customWidth="1"/>
-    <col min="38" max="38" width="10.5" style="25" customWidth="1"/>
-    <col min="39" max="41" width="16.1640625" style="25" customWidth="1"/>
-    <col min="42" max="42" width="9.5" style="25" customWidth="1"/>
-    <col min="43" max="43" width="8.83203125" style="25" customWidth="1"/>
-    <col min="44" max="46" width="16.1640625" style="25" customWidth="1"/>
+    <col min="38" max="38" width="10.42578125" style="25" customWidth="1"/>
+    <col min="39" max="41" width="16.140625" style="25" customWidth="1"/>
+    <col min="42" max="42" width="9.42578125" style="25" customWidth="1"/>
+    <col min="43" max="43" width="8.85546875" style="25" customWidth="1"/>
+    <col min="44" max="46" width="16.140625" style="25" customWidth="1"/>
     <col min="47" max="47" width="2" customWidth="1"/>
-    <col min="48" max="48" width="15.6640625" customWidth="1"/>
-    <col min="49" max="60" width="13.83203125" customWidth="1"/>
+    <col min="48" max="48" width="15.7109375" customWidth="1"/>
+    <col min="49" max="60" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:60" ht="11.25" thickBot="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:60" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:60" ht="10.8" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:60" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="14" t="s">
         <v>259</v>
       </c>
@@ -24202,7 +24202,7 @@
       <c r="AT2" s="15"/>
       <c r="AU2" s="15"/>
     </row>
-    <row r="3" spans="2:60" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:60" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>23</v>
       </c>
@@ -24256,7 +24256,7 @@
       <c r="AT3" s="34"/>
       <c r="AU3" s="34"/>
     </row>
-    <row r="4" spans="2:60" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:60" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -24310,7 +24310,7 @@
       <c r="AT4" s="5"/>
       <c r="AU4" s="5"/>
     </row>
-    <row r="5" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="5" spans="2:60" x14ac:dyDescent="0.2">
       <c r="V5"/>
       <c r="W5"/>
       <c r="X5"/>
@@ -24337,46 +24337,46 @@
       <c r="AS5"/>
       <c r="AT5"/>
     </row>
-    <row r="6" spans="2:60" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:60" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="391" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="398" t="s">
+      <c r="C6" s="402" t="s">
         <v>29</v>
       </c>
       <c r="D6" s="444" t="s">
         <v>111</v>
       </c>
-      <c r="E6" s="399" t="s">
+      <c r="E6" s="403" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="400"/>
+      <c r="F6" s="404"/>
       <c r="G6" s="431" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="409" t="s">
+      <c r="H6" s="413" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="409"/>
-      <c r="J6" s="409"/>
-      <c r="K6" s="409"/>
-      <c r="L6" s="414" t="s">
+      <c r="I6" s="413"/>
+      <c r="J6" s="413"/>
+      <c r="K6" s="413"/>
+      <c r="L6" s="418" t="s">
         <v>32</v>
       </c>
-      <c r="M6" s="415"/>
-      <c r="N6" s="416"/>
-      <c r="O6" s="417" t="s">
+      <c r="M6" s="419"/>
+      <c r="N6" s="420"/>
+      <c r="O6" s="421" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="419"/>
-      <c r="Q6" s="420" t="s">
+      <c r="P6" s="423"/>
+      <c r="Q6" s="396" t="s">
         <v>34</v>
       </c>
-      <c r="R6" s="421"/>
-      <c r="S6" s="420" t="s">
+      <c r="R6" s="397"/>
+      <c r="S6" s="396" t="s">
         <v>35</v>
       </c>
-      <c r="T6" s="421"/>
+      <c r="T6" s="397"/>
       <c r="U6" s="392" t="s">
         <v>36</v>
       </c>
@@ -24417,51 +24417,51 @@
       <c r="AT6" s="439"/>
       <c r="AU6" s="42"/>
     </row>
-    <row r="7" spans="2:60" s="6" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:60" s="6" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="391"/>
-      <c r="C7" s="398"/>
+      <c r="C7" s="402"/>
       <c r="D7" s="445"/>
-      <c r="E7" s="401"/>
-      <c r="F7" s="402"/>
+      <c r="E7" s="405"/>
+      <c r="F7" s="406"/>
       <c r="G7" s="432"/>
-      <c r="H7" s="410">
+      <c r="H7" s="414">
         <v>43100</v>
       </c>
-      <c r="I7" s="411" t="s">
+      <c r="I7" s="415" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="411" t="s">
+      <c r="J7" s="415" t="s">
         <v>39</v>
       </c>
       <c r="K7" s="44">
         <v>43465</v>
       </c>
-      <c r="L7" s="411" t="s">
+      <c r="L7" s="415" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="411" t="s">
+      <c r="M7" s="415" t="s">
         <v>9</v>
       </c>
       <c r="N7" s="44">
         <f>K7</f>
         <v>43465</v>
       </c>
-      <c r="O7" s="422" t="s">
+      <c r="O7" s="394" t="s">
         <v>43</v>
       </c>
-      <c r="P7" s="422" t="s">
+      <c r="P7" s="394" t="s">
         <v>42</v>
       </c>
-      <c r="Q7" s="422" t="s">
+      <c r="Q7" s="394" t="s">
         <v>42</v>
       </c>
-      <c r="R7" s="422" t="s">
+      <c r="R7" s="394" t="s">
         <v>43</v>
       </c>
-      <c r="S7" s="422" t="s">
+      <c r="S7" s="394" t="s">
         <v>42</v>
       </c>
-      <c r="T7" s="422" t="s">
+      <c r="T7" s="394" t="s">
         <v>43</v>
       </c>
       <c r="U7" s="392"/>
@@ -24571,30 +24571,30 @@
         <v>271</v>
       </c>
     </row>
-    <row r="8" spans="2:60" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:60" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="391"/>
-      <c r="C8" s="398"/>
+      <c r="C8" s="402"/>
       <c r="D8" s="446"/>
-      <c r="E8" s="403"/>
-      <c r="F8" s="404"/>
+      <c r="E8" s="407"/>
+      <c r="F8" s="408"/>
       <c r="G8" s="433"/>
-      <c r="H8" s="411"/>
-      <c r="I8" s="411"/>
-      <c r="J8" s="411"/>
+      <c r="H8" s="415"/>
+      <c r="I8" s="415"/>
+      <c r="J8" s="415"/>
       <c r="K8" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="411"/>
-      <c r="M8" s="411"/>
+      <c r="L8" s="415"/>
+      <c r="M8" s="415"/>
       <c r="N8" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="O8" s="423"/>
-      <c r="P8" s="423"/>
-      <c r="Q8" s="423"/>
-      <c r="R8" s="423"/>
-      <c r="S8" s="423"/>
-      <c r="T8" s="423"/>
+      <c r="O8" s="395"/>
+      <c r="P8" s="395"/>
+      <c r="Q8" s="395"/>
+      <c r="R8" s="395"/>
+      <c r="S8" s="395"/>
+      <c r="T8" s="395"/>
       <c r="U8" s="392"/>
       <c r="V8" s="441"/>
       <c r="W8" s="278"/>
@@ -24638,7 +24638,7 @@
       <c r="BG8" s="199"/>
       <c r="BH8" s="199"/>
     </row>
-    <row r="9" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B9" s="52"/>
       <c r="C9" s="53"/>
       <c r="D9" s="54"/>
@@ -24686,7 +24686,7 @@
       <c r="AT9" s="60"/>
       <c r="AU9" s="60"/>
     </row>
-    <row r="10" spans="2:60" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:60" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B10" s="61"/>
       <c r="C10" s="62" t="s">
         <v>14</v>
@@ -24749,7 +24749,7 @@
       <c r="BG10" s="208"/>
       <c r="BH10" s="208"/>
     </row>
-    <row r="11" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B11" s="68"/>
       <c r="C11" s="69"/>
       <c r="D11" s="70"/>
@@ -24797,7 +24797,7 @@
       <c r="AT11" s="60"/>
       <c r="AU11" s="60"/>
     </row>
-    <row r="12" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B12" s="68"/>
       <c r="C12" s="89">
         <v>39157</v>
@@ -25004,7 +25004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B13" s="68"/>
       <c r="C13" s="89">
         <v>39157</v>
@@ -25211,7 +25211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B14" s="68"/>
       <c r="C14" s="89">
         <v>39157</v>
@@ -25418,7 +25418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B15" s="68"/>
       <c r="C15" s="89">
         <v>39157</v>
@@ -25625,7 +25625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B16" s="68"/>
       <c r="C16" s="89">
         <v>39157</v>
@@ -25832,7 +25832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B17" s="68"/>
       <c r="C17" s="89">
         <v>39294</v>
@@ -26039,7 +26039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B18" s="68"/>
       <c r="C18" s="89">
         <v>39314</v>
@@ -26246,7 +26246,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B19" s="68"/>
       <c r="C19" s="89">
         <v>39342</v>
@@ -26453,7 +26453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B20" s="68"/>
       <c r="C20" s="89">
         <v>39463</v>
@@ -26660,7 +26660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B21" s="68"/>
       <c r="C21" s="89">
         <v>39506</v>
@@ -26867,7 +26867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B22" s="68"/>
       <c r="C22" s="89">
         <v>39552</v>
@@ -27074,7 +27074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B23" s="68"/>
       <c r="C23" s="89">
         <v>39574</v>
@@ -27281,7 +27281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B24" s="68"/>
       <c r="C24" s="89">
         <v>39577</v>
@@ -27488,7 +27488,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B25" s="68"/>
       <c r="C25" s="89">
         <v>39577</v>
@@ -27695,7 +27695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B26" s="68"/>
       <c r="C26" s="89">
         <v>39589</v>
@@ -27902,7 +27902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B27" s="68"/>
       <c r="C27" s="89">
         <v>39593</v>
@@ -28109,7 +28109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B28" s="68"/>
       <c r="C28" s="89">
         <v>39594</v>
@@ -28316,7 +28316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B29" s="68"/>
       <c r="C29" s="89">
         <v>39644</v>
@@ -28523,7 +28523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B30" s="68"/>
       <c r="C30" s="89">
         <v>39841</v>
@@ -28730,7 +28730,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B31" s="68"/>
       <c r="C31" s="89">
         <v>39841</v>
@@ -28937,7 +28937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B32" s="68"/>
       <c r="C32" s="89">
         <v>40318</v>
@@ -29144,7 +29144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B33" s="68"/>
       <c r="C33" s="89">
         <v>40318</v>
@@ -29351,7 +29351,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B34" s="68"/>
       <c r="C34" s="89">
         <v>40332</v>
@@ -29558,7 +29558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B35" s="68"/>
       <c r="C35" s="89">
         <v>40612</v>
@@ -29765,7 +29765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B36" s="68"/>
       <c r="C36" s="89">
         <v>40612</v>
@@ -29972,7 +29972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B37" s="68"/>
       <c r="C37" s="89">
         <v>40847</v>
@@ -30179,7 +30179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B38" s="68"/>
       <c r="C38" s="89">
         <v>40851</v>
@@ -30386,7 +30386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B39" s="68"/>
       <c r="C39" s="89">
         <v>40858</v>
@@ -30593,7 +30593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B40" s="68"/>
       <c r="C40" s="89">
         <v>40891</v>
@@ -30800,7 +30800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B41" s="68"/>
       <c r="C41" s="89">
         <v>40547</v>
@@ -31007,7 +31007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B42" s="68"/>
       <c r="C42" s="89">
         <v>40569</v>
@@ -31214,7 +31214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B43" s="68"/>
       <c r="C43" s="89">
         <v>40569</v>
@@ -31421,7 +31421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B44" s="68"/>
       <c r="C44" s="89">
         <v>40984</v>
@@ -31628,7 +31628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B45" s="68"/>
       <c r="C45" s="89">
         <v>41194</v>
@@ -31835,7 +31835,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B46" s="68"/>
       <c r="C46" s="89">
         <v>41205</v>
@@ -32042,7 +32042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B47" s="68"/>
       <c r="C47" s="89">
         <v>41204</v>
@@ -32249,7 +32249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B48" s="68"/>
       <c r="C48" s="89">
         <v>41108</v>
@@ -32456,7 +32456,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B49" s="68"/>
       <c r="C49" s="89">
         <v>41124</v>
@@ -32663,7 +32663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B50" s="68"/>
       <c r="C50" s="89">
         <v>41166</v>
@@ -32870,7 +32870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B51" s="68"/>
       <c r="C51" s="89">
         <v>41214</v>
@@ -33077,7 +33077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B52" s="68"/>
       <c r="C52" s="89">
         <v>41355</v>
@@ -33284,7 +33284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B53" s="68"/>
       <c r="C53" s="89">
         <v>41479</v>
@@ -33491,7 +33491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B54" s="68"/>
       <c r="C54" s="89">
         <v>41521</v>
@@ -33698,7 +33698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B55" s="68"/>
       <c r="C55" s="89">
         <v>41575</v>
@@ -33905,7 +33905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B56" s="68"/>
       <c r="C56" s="89">
         <v>41592</v>
@@ -34112,7 +34112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B57" s="68"/>
       <c r="C57" s="89">
         <v>41723</v>
@@ -34319,7 +34319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B58" s="68"/>
       <c r="C58" s="89">
         <v>41766</v>
@@ -34526,7 +34526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B59" s="68"/>
       <c r="C59" s="89">
         <v>41780</v>
@@ -34733,7 +34733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B60" s="68"/>
       <c r="C60" s="89">
         <v>41817</v>
@@ -34940,7 +34940,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B61" s="68"/>
       <c r="C61" s="89">
         <v>41817</v>
@@ -35147,7 +35147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B62" s="68"/>
       <c r="C62" s="89">
         <v>41832</v>
@@ -35354,7 +35354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B63" s="68"/>
       <c r="C63" s="89">
         <v>41858</v>
@@ -35561,7 +35561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B64" s="68"/>
       <c r="C64" s="89">
         <v>41863</v>
@@ -35768,7 +35768,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B65" s="68"/>
       <c r="C65" s="89">
         <v>41877</v>
@@ -35975,7 +35975,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B66" s="68"/>
       <c r="C66" s="89">
         <v>41878</v>
@@ -36182,7 +36182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B67" s="68"/>
       <c r="C67" s="89">
         <v>41902</v>
@@ -36389,7 +36389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B68" s="68"/>
       <c r="C68" s="89">
         <v>41902</v>
@@ -36596,7 +36596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B69" s="68"/>
       <c r="C69" s="89">
         <v>41902</v>
@@ -36803,7 +36803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B70" s="68"/>
       <c r="C70" s="89">
         <v>41928</v>
@@ -37010,7 +37010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B71" s="68"/>
       <c r="C71" s="89">
         <v>42027</v>
@@ -37217,7 +37217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B72" s="68"/>
       <c r="C72" s="89">
         <v>42037</v>
@@ -37424,7 +37424,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B73" s="68"/>
       <c r="C73" s="89">
         <v>42052</v>
@@ -37631,7 +37631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B74" s="68"/>
       <c r="C74" s="89">
         <v>42053</v>
@@ -37838,7 +37838,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B75" s="68"/>
       <c r="C75" s="89">
         <v>42053</v>
@@ -38045,7 +38045,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B76" s="68"/>
       <c r="C76" s="89">
         <v>42039</v>
@@ -38252,7 +38252,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B77" s="68"/>
       <c r="C77" s="89">
         <v>42075</v>
@@ -38459,7 +38459,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B78" s="68"/>
       <c r="C78" s="89">
         <v>42075</v>
@@ -38666,7 +38666,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B79" s="68"/>
       <c r="C79" s="89">
         <v>42093</v>
@@ -38873,7 +38873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B80" s="68"/>
       <c r="C80" s="89">
         <v>42118</v>
@@ -39080,7 +39080,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B81" s="68"/>
       <c r="C81" s="89">
         <v>42123</v>
@@ -39287,7 +39287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B82" s="68"/>
       <c r="C82" s="89">
         <v>42146</v>
@@ -39494,7 +39494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B83" s="68"/>
       <c r="C83" s="89">
         <v>42171</v>
@@ -39701,7 +39701,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B84" s="68"/>
       <c r="C84" s="89">
         <v>42194</v>
@@ -39908,7 +39908,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B85" s="68"/>
       <c r="C85" s="89">
         <v>42186</v>
@@ -40115,7 +40115,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B86" s="68"/>
       <c r="C86" s="89">
         <v>42215</v>
@@ -40322,7 +40322,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B87" s="68"/>
       <c r="C87" s="89">
         <v>42246</v>
@@ -40529,7 +40529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B88" s="68"/>
       <c r="C88" s="89">
         <v>42348</v>
@@ -40736,7 +40736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B89" s="68"/>
       <c r="C89" s="89">
         <v>42340</v>
@@ -40943,7 +40943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B90" s="68"/>
       <c r="C90" s="89">
         <v>42460</v>
@@ -41150,7 +41150,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B91" s="68"/>
       <c r="C91" s="89">
         <v>42480</v>
@@ -41357,7 +41357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B92" s="68"/>
       <c r="C92" s="89">
         <v>42493</v>
@@ -41564,7 +41564,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B93" s="68"/>
       <c r="C93" s="89">
         <v>42605</v>
@@ -41771,7 +41771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="94" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B94" s="68"/>
       <c r="C94" s="89">
         <v>42621</v>
@@ -41978,7 +41978,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B95" s="68"/>
       <c r="C95" s="89">
         <v>42634</v>
@@ -42185,7 +42185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B96" s="68"/>
       <c r="C96" s="89">
         <v>42647</v>
@@ -42392,7 +42392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="97" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B97" s="68"/>
       <c r="C97" s="89">
         <v>42678</v>
@@ -42601,7 +42601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="98" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B98" s="68"/>
       <c r="C98" s="89">
         <v>42695</v>
@@ -42810,7 +42810,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="99" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B99" s="68"/>
       <c r="C99" s="89">
         <v>42751</v>
@@ -43019,7 +43019,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="100" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B100" s="68"/>
       <c r="C100" s="89">
         <v>42789</v>
@@ -43228,7 +43228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="101" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B101" s="68"/>
       <c r="C101" s="89">
         <v>42807</v>
@@ -43437,7 +43437,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B102" s="68"/>
       <c r="C102" s="89">
         <v>42863</v>
@@ -43646,7 +43646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B103" s="68"/>
       <c r="C103" s="89">
         <v>42867</v>
@@ -43855,7 +43855,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="104" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B104" s="68"/>
       <c r="C104" s="89">
         <v>42901</v>
@@ -44064,7 +44064,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="105" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B105" s="68"/>
       <c r="C105" s="89">
         <v>42942</v>
@@ -44273,7 +44273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="106" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B106" s="68"/>
       <c r="C106" s="89">
         <v>42956</v>
@@ -44482,7 +44482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="107" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B107" s="68"/>
       <c r="C107" s="89">
         <v>42956</v>
@@ -44691,7 +44691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="108" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B108" s="68"/>
       <c r="C108" s="89">
         <v>42970</v>
@@ -44900,7 +44900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="109" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B109" s="68"/>
       <c r="C109" s="89">
         <v>43008</v>
@@ -45109,7 +45109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="110" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B110" s="68"/>
       <c r="C110" s="89">
         <v>43008</v>
@@ -45318,7 +45318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="111" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B111" s="68"/>
       <c r="C111" s="89">
         <v>43059</v>
@@ -45527,7 +45527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="112" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B112" s="68"/>
       <c r="C112" s="89">
         <v>43087</v>
@@ -45736,7 +45736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="113" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B113" s="68"/>
       <c r="C113" s="89">
         <v>43100</v>
@@ -45945,7 +45945,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="114" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B114" s="97"/>
       <c r="C114" s="98">
         <v>43116</v>
@@ -46154,7 +46154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="115" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B115" s="97"/>
       <c r="C115" s="98">
         <v>43116</v>
@@ -46363,7 +46363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="116" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B116" s="97"/>
       <c r="C116" s="98">
         <v>43154</v>
@@ -46572,7 +46572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="117" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B117" s="97"/>
       <c r="C117" s="98">
         <v>43159</v>
@@ -46781,7 +46781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="118" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B118" s="97"/>
       <c r="C118" s="98">
         <v>43179</v>
@@ -46990,7 +46990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="119" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B119" s="97"/>
       <c r="C119" s="98">
         <v>43182</v>
@@ -47199,7 +47199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="120" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B120" s="97"/>
       <c r="C120" s="98">
         <v>43251</v>
@@ -47408,7 +47408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="121" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B121" s="97"/>
       <c r="C121" s="98">
         <v>43259</v>
@@ -47617,7 +47617,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="122" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B122" s="97"/>
       <c r="C122" s="98">
         <v>43256</v>
@@ -47826,7 +47826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="123" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B123" s="97"/>
       <c r="C123" s="98">
         <v>43307</v>
@@ -48035,7 +48035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="124" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B124" s="97"/>
       <c r="C124" s="98">
         <v>43402</v>
@@ -48244,7 +48244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="125" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B125" s="97"/>
       <c r="C125" s="98">
         <v>43402</v>
@@ -48453,7 +48453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="126" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B126" s="97"/>
       <c r="C126" s="98"/>
       <c r="D126" s="99"/>
@@ -48514,7 +48514,7 @@
       <c r="BG126" s="172"/>
       <c r="BH126" s="172"/>
     </row>
-    <row r="127" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="127" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B127" s="68"/>
       <c r="C127" s="257">
         <v>43473</v>
@@ -48717,7 +48717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="128" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B128" s="68"/>
       <c r="C128" s="257">
         <v>43503</v>
@@ -48920,7 +48920,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="129" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B129" s="68"/>
       <c r="C129" s="257">
         <v>43525</v>
@@ -49123,7 +49123,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="130" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B130" s="68"/>
       <c r="C130" s="257">
         <v>43626</v>
@@ -49326,7 +49326,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="131" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B131" s="68"/>
       <c r="C131" s="257">
         <v>43650</v>
@@ -49529,7 +49529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="132" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B132" s="68"/>
       <c r="C132" s="257">
         <v>43762</v>
@@ -49732,7 +49732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="133" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B133" s="68"/>
       <c r="C133" s="257"/>
       <c r="D133" s="258"/>
@@ -49793,7 +49793,7 @@
       <c r="BG133" s="172"/>
       <c r="BH133" s="172"/>
     </row>
-    <row r="134" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="134" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B134" s="68"/>
       <c r="C134" s="257">
         <v>43980</v>
@@ -49996,7 +49996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="135" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B135" s="68"/>
       <c r="C135" s="257">
         <v>43980</v>
@@ -50199,7 +50199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="136" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B136" s="68"/>
       <c r="C136" s="257">
         <v>43992</v>
@@ -50402,7 +50402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="137" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B137" s="68"/>
       <c r="C137" s="257">
         <v>43993</v>
@@ -50605,7 +50605,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="138" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B138" s="68"/>
       <c r="C138" s="257">
         <v>44002</v>
@@ -50808,7 +50808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="139" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B139" s="68"/>
       <c r="C139" s="257">
         <v>44035</v>
@@ -51011,7 +51011,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="140" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B140" s="68"/>
       <c r="C140" s="257">
         <v>44040</v>
@@ -51214,7 +51214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="141" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B141" s="68"/>
       <c r="C141" s="239"/>
       <c r="D141" s="99"/>
@@ -51275,7 +51275,7 @@
       <c r="BG141" s="172"/>
       <c r="BH141" s="172"/>
     </row>
-    <row r="142" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="142" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B142" s="68"/>
       <c r="C142" s="239"/>
       <c r="D142" s="99"/>
@@ -51426,7 +51426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="143" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B143" s="68"/>
       <c r="C143" s="239"/>
       <c r="D143" s="99"/>
@@ -51487,7 +51487,7 @@
       <c r="BG143" s="172"/>
       <c r="BH143" s="172"/>
     </row>
-    <row r="144" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="144" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B144" s="68"/>
       <c r="C144" s="89">
         <v>44244</v>
@@ -51692,7 +51692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="145" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B145" s="68"/>
       <c r="C145" s="89">
         <v>44251</v>
@@ -51897,7 +51897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="146" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B146" s="68"/>
       <c r="C146" s="89">
         <v>44285</v>
@@ -52102,7 +52102,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="147" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B147" s="68"/>
       <c r="C147" s="89">
         <v>44326</v>
@@ -52307,7 +52307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="148" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B148" s="68"/>
       <c r="C148" s="89">
         <v>44354</v>
@@ -52512,7 +52512,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="149" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B149" s="68"/>
       <c r="C149" s="89">
         <v>44354</v>
@@ -52717,7 +52717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="150" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B150" s="68"/>
       <c r="C150" s="89">
         <v>44354</v>
@@ -52922,7 +52922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="151" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B151" s="68"/>
       <c r="C151" s="89">
         <v>44354</v>
@@ -53127,7 +53127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="152" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B152" s="68"/>
       <c r="C152" s="89">
         <v>44354</v>
@@ -53332,7 +53332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="153" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B153" s="68"/>
       <c r="C153" s="89">
         <v>44368</v>
@@ -53537,7 +53537,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="154" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B154" s="68"/>
       <c r="C154" s="89">
         <v>44412</v>
@@ -53742,7 +53742,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="155" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B155" s="68"/>
       <c r="C155" s="89">
         <v>44446</v>
@@ -53947,7 +53947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="156" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B156" s="68"/>
       <c r="C156" s="89">
         <v>44456</v>
@@ -54152,7 +54152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="157" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B157" s="68"/>
       <c r="C157" s="89">
         <v>44459</v>
@@ -54355,7 +54355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="158" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B158" s="68"/>
       <c r="C158" s="89">
         <v>44482</v>
@@ -54558,7 +54558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="159" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B159" s="68"/>
       <c r="C159" s="89">
         <v>44530</v>
@@ -54763,7 +54763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="160" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B160" s="68"/>
       <c r="C160" s="89">
         <v>44552</v>
@@ -54968,7 +54968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="161" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B161" s="68"/>
       <c r="C161" s="89"/>
       <c r="D161" s="70"/>
@@ -55017,7 +55017,7 @@
       <c r="AU161" s="60"/>
       <c r="AV161" s="196"/>
     </row>
-    <row r="162" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="162" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B162" s="68"/>
       <c r="C162" s="89"/>
       <c r="D162" s="70"/>
@@ -55168,7 +55168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="163" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B163" s="68"/>
       <c r="C163" s="89"/>
       <c r="D163" s="70"/>
@@ -55229,7 +55229,7 @@
       <c r="BG163" s="252"/>
       <c r="BH163" s="252"/>
     </row>
-    <row r="164" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="164" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B164" s="68"/>
       <c r="C164" s="89">
         <v>44575</v>
@@ -55434,7 +55434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="165" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B165" s="68"/>
       <c r="C165" s="89">
         <v>44651</v>
@@ -55639,7 +55639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="166" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B166" s="68"/>
       <c r="C166" s="89">
         <v>44749</v>
@@ -55844,7 +55844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="167" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B167" s="68"/>
       <c r="C167" s="89">
         <v>44792</v>
@@ -56049,7 +56049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="168" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B168" s="68"/>
       <c r="C168" s="89">
         <v>44917</v>
@@ -56254,7 +56254,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="169" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B169" s="68"/>
       <c r="C169" s="89"/>
       <c r="D169" s="268"/>
@@ -56455,7 +56455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="170" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B170" s="68"/>
       <c r="C170" s="89"/>
       <c r="D170" s="268"/>
@@ -56516,7 +56516,7 @@
       <c r="BG170" s="252"/>
       <c r="BH170" s="252"/>
     </row>
-    <row r="171" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="171" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B171" s="68"/>
       <c r="C171" s="89"/>
       <c r="D171" s="70"/>
@@ -56667,7 +56667,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="172" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B172" s="68"/>
       <c r="C172" s="89"/>
       <c r="D172" s="70"/>
@@ -56728,7 +56728,7 @@
       <c r="BG172" s="252"/>
       <c r="BH172" s="252"/>
     </row>
-    <row r="173" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="173" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B173" s="68"/>
       <c r="C173" s="89">
         <v>44956</v>
@@ -56921,7 +56921,7 @@
         <v>131250</v>
       </c>
     </row>
-    <row r="174" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="174" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B174" s="68"/>
       <c r="C174" s="89">
         <v>45100</v>
@@ -57114,7 +57114,7 @@
         <v>179166.66666666666</v>
       </c>
     </row>
-    <row r="175" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="175" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B175" s="68"/>
       <c r="C175" s="89">
         <v>45113</v>
@@ -57307,7 +57307,7 @@
         <v>58312.5</v>
       </c>
     </row>
-    <row r="176" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="176" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B176" s="68"/>
       <c r="C176" s="89">
         <v>45125</v>
@@ -57500,7 +57500,7 @@
         <v>151041.66666666666</v>
       </c>
     </row>
-    <row r="177" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="177" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B177" s="68"/>
       <c r="C177" s="89">
         <v>45138</v>
@@ -57693,7 +57693,7 @@
         <v>153125</v>
       </c>
     </row>
-    <row r="178" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="178" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B178" s="68"/>
       <c r="C178" s="89">
         <v>45193</v>
@@ -57886,7 +57886,7 @@
         <v>98968.75</v>
       </c>
     </row>
-    <row r="179" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="179" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B179" s="68"/>
       <c r="C179" s="89">
         <v>45230</v>
@@ -58079,7 +58079,7 @@
         <v>158333.33333333334</v>
       </c>
     </row>
-    <row r="180" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="180" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B180" s="68"/>
       <c r="C180" s="89"/>
       <c r="D180" s="70"/>
@@ -58140,7 +58140,7 @@
       <c r="BG180" s="252"/>
       <c r="BH180" s="252"/>
     </row>
-    <row r="181" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="181" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B181" s="68"/>
       <c r="C181" s="89"/>
       <c r="D181" s="70"/>
@@ -58282,7 +58282,7 @@
         <v>930197.91666666663</v>
       </c>
     </row>
-    <row r="182" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="182" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B182" s="68"/>
       <c r="C182" s="89"/>
       <c r="D182" s="70"/>
@@ -58343,7 +58343,7 @@
       <c r="BG182" s="252"/>
       <c r="BH182" s="252"/>
     </row>
-    <row r="183" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="183" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B183" s="68"/>
       <c r="C183" s="328">
         <v>45384</v>
@@ -58524,7 +58524,7 @@
         <v>22916.666666666668</v>
       </c>
     </row>
-    <row r="184" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="184" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B184" s="68"/>
       <c r="C184" s="328">
         <v>45481</v>
@@ -58705,7 +58705,7 @@
         <v>178847.60416666666</v>
       </c>
     </row>
-    <row r="185" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="185" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B185" s="68"/>
       <c r="C185" s="328">
         <v>45481</v>
@@ -58886,7 +58886,7 @@
         <v>156325.0625</v>
       </c>
     </row>
-    <row r="186" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="186" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B186" s="68"/>
       <c r="C186" s="328">
         <v>45482</v>
@@ -59067,7 +59067,7 @@
         <v>86413.875</v>
       </c>
     </row>
-    <row r="187" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="187" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B187" s="68"/>
       <c r="C187" s="328">
         <v>45523</v>
@@ -59248,7 +59248,7 @@
         <v>235416.66666666666</v>
       </c>
     </row>
-    <row r="188" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="188" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B188" s="68"/>
       <c r="C188" s="328">
         <v>45540</v>
@@ -59429,7 +59429,7 @@
         <v>269541.66666666669</v>
       </c>
     </row>
-    <row r="189" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="189" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B189" s="68"/>
       <c r="C189" s="328">
         <v>45565</v>
@@ -59610,7 +59610,7 @@
         <v>79145.833333333328</v>
       </c>
     </row>
-    <row r="190" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="190" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B190" s="68"/>
       <c r="C190" s="328">
         <v>45616</v>
@@ -59791,7 +59791,7 @@
         <v>167023.27083333334</v>
       </c>
     </row>
-    <row r="191" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="191" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B191" s="68"/>
       <c r="C191" s="328">
         <v>45616</v>
@@ -59972,7 +59972,7 @@
         <v>43168.166666666664</v>
       </c>
     </row>
-    <row r="192" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="192" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B192" s="68"/>
       <c r="C192" s="328"/>
       <c r="D192" s="363"/>
@@ -60033,7 +60033,7 @@
       <c r="BG192" s="325"/>
       <c r="BH192" s="325"/>
     </row>
-    <row r="193" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="193" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B193" s="68"/>
       <c r="C193" s="328"/>
       <c r="D193" s="363"/>
@@ -60166,7 +60166,7 @@
         <v>1238798.8125000002</v>
       </c>
     </row>
-    <row r="194" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="194" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B194" s="68"/>
       <c r="C194" s="328"/>
       <c r="D194" s="363"/>
@@ -60227,7 +60227,7 @@
       <c r="BG194" s="366"/>
       <c r="BH194" s="366"/>
     </row>
-    <row r="195" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="195" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B195" s="68"/>
       <c r="C195" s="89">
         <v>45672</v>
@@ -60391,7 +60391,7 @@
         <v>161621.97916666666</v>
       </c>
     </row>
-    <row r="196" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="196" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B196" s="68"/>
       <c r="C196" s="89">
         <v>45680</v>
@@ -60557,7 +60557,7 @@
         <v>97295.833333333328</v>
       </c>
     </row>
-    <row r="197" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="197" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B197" s="68"/>
       <c r="C197" s="89">
         <v>45681</v>
@@ -60723,7 +60723,7 @@
         <v>77223.166666666672</v>
       </c>
     </row>
-    <row r="198" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="198" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B198" s="68"/>
       <c r="C198" s="89">
         <v>45730</v>
@@ -60889,7 +60889,7 @@
         <v>91666.666666666672</v>
       </c>
     </row>
-    <row r="199" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="199" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B199" s="68"/>
       <c r="C199" s="89">
         <v>45777</v>
@@ -61055,7 +61055,7 @@
         <v>52552.583333333336</v>
       </c>
     </row>
-    <row r="200" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="200" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B200" s="68"/>
       <c r="C200" s="89">
         <v>45827</v>
@@ -61221,7 +61221,7 @@
         <v>46447.916666666664</v>
       </c>
     </row>
-    <row r="201" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="201" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B201" s="68"/>
       <c r="C201" s="89">
         <v>45917</v>
@@ -61387,7 +61387,7 @@
         <v>393054.16666666669</v>
       </c>
     </row>
-    <row r="202" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="202" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B202" s="68"/>
       <c r="C202" s="89">
         <v>45923</v>
@@ -61553,7 +61553,7 @@
         <v>49753.229166666664</v>
       </c>
     </row>
-    <row r="203" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="203" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B203" s="68"/>
       <c r="C203" s="89">
         <v>45967</v>
@@ -61719,7 +61719,7 @@
         <v>43195.833333333336</v>
       </c>
     </row>
-    <row r="204" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="204" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B204" s="68"/>
       <c r="C204" s="89">
         <v>46014</v>
@@ -61885,7 +61885,7 @@
         <v>78125</v>
       </c>
     </row>
-    <row r="205" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="205" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B205" s="68"/>
       <c r="C205" s="89"/>
       <c r="D205" s="70"/>
@@ -61946,7 +61946,7 @@
       <c r="BG205" s="252"/>
       <c r="BH205" s="252"/>
     </row>
-    <row r="206" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="206" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B206" s="68"/>
       <c r="C206" s="89"/>
       <c r="D206" s="70"/>
@@ -62070,7 +62070,7 @@
         <v>1090936.375</v>
       </c>
     </row>
-    <row r="207" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="207" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B207" s="68"/>
       <c r="C207" s="89"/>
       <c r="D207" s="70"/>
@@ -62131,7 +62131,7 @@
       <c r="BG207" s="252"/>
       <c r="BH207" s="252"/>
     </row>
-    <row r="208" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="208" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B208" s="68"/>
       <c r="C208" s="89">
         <v>46030</v>
@@ -62282,7 +62282,7 @@
         <v>165625</v>
       </c>
     </row>
-    <row r="209" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="209" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B209" s="68"/>
       <c r="C209" s="89">
         <v>46037</v>
@@ -62433,7 +62433,7 @@
         <v>16354.166666666666</v>
       </c>
     </row>
-    <row r="210" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="210" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B210" s="68"/>
       <c r="C210" s="89"/>
       <c r="D210" s="70"/>
@@ -62494,7 +62494,7 @@
       <c r="BG210" s="252"/>
       <c r="BH210" s="252"/>
     </row>
-    <row r="211" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="211" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B211" s="68"/>
       <c r="C211" s="89"/>
       <c r="D211" s="70"/>
@@ -62555,7 +62555,7 @@
       <c r="BG211" s="252"/>
       <c r="BH211" s="252"/>
     </row>
-    <row r="212" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="212" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B212" s="68"/>
       <c r="C212" s="89"/>
       <c r="D212" s="70"/>
@@ -62670,7 +62670,7 @@
         <v>181979.16666666666</v>
       </c>
     </row>
-    <row r="213" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="213" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B213" s="68"/>
       <c r="C213" s="89"/>
       <c r="D213" s="70"/>
@@ -62731,7 +62731,7 @@
       <c r="BG213" s="252"/>
       <c r="BH213" s="252"/>
     </row>
-    <row r="214" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="214" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B214" s="68"/>
       <c r="C214" s="89"/>
       <c r="D214" s="70"/>
@@ -62882,7 +62882,7 @@
         <v>3441912.2708333335</v>
       </c>
     </row>
-    <row r="215" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="215" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B215" s="68"/>
       <c r="C215" s="89"/>
       <c r="D215" s="70"/>
@@ -62931,7 +62931,7 @@
       <c r="AU215" s="60"/>
       <c r="AV215" s="301"/>
     </row>
-    <row r="216" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="216" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B216" s="10" t="s">
         <v>65</v>
       </c>
@@ -62976,7 +62976,7 @@
       <c r="BC216" s="12"/>
       <c r="BD216" s="25"/>
     </row>
-    <row r="217" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="217" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B217" s="10"/>
       <c r="E217" s="165"/>
       <c r="G217"/>
@@ -63019,7 +63019,7 @@
       <c r="BC217" s="12"/>
       <c r="BD217" s="25"/>
     </row>
-    <row r="218" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="218" spans="2:60" x14ac:dyDescent="0.2">
       <c r="C218" s="173" t="s">
         <v>12</v>
       </c>
@@ -63063,7 +63063,7 @@
       <c r="BC218" s="12"/>
       <c r="BD218" s="25"/>
     </row>
-    <row r="219" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="219" spans="2:60" x14ac:dyDescent="0.2">
       <c r="C219" s="172" t="s">
         <v>46</v>
       </c>
@@ -63110,7 +63110,7 @@
       <c r="BC219" s="12"/>
       <c r="BD219" s="25"/>
     </row>
-    <row r="220" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="220" spans="2:60" x14ac:dyDescent="0.2">
       <c r="C220" s="172" t="s">
         <v>66</v>
       </c>
@@ -63157,7 +63157,7 @@
       <c r="BC220" s="12"/>
       <c r="BD220" s="25"/>
     </row>
-    <row r="221" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="221" spans="2:60" x14ac:dyDescent="0.2">
       <c r="C221" s="172"/>
       <c r="E221" s="165"/>
       <c r="G221"/>
@@ -63202,7 +63202,7 @@
       <c r="BC221" s="12"/>
       <c r="BD221" s="25"/>
     </row>
-    <row r="222" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="222" spans="2:60" x14ac:dyDescent="0.2">
       <c r="E222" s="165"/>
       <c r="G222"/>
       <c r="H222" s="166"/>
@@ -63243,7 +63243,7 @@
       <c r="BC222" s="12"/>
       <c r="BD222" s="25"/>
     </row>
-    <row r="223" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="223" spans="2:60" x14ac:dyDescent="0.2">
       <c r="E223" s="165"/>
       <c r="G223"/>
       <c r="H223" s="166"/>
@@ -63284,7 +63284,7 @@
       <c r="BC223" s="12"/>
       <c r="BD223" s="25"/>
     </row>
-    <row r="224" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="224" spans="2:60" x14ac:dyDescent="0.2">
       <c r="C224" s="173" t="s">
         <v>25</v>
       </c>
@@ -63328,7 +63328,7 @@
       <c r="BC224" s="12"/>
       <c r="BD224" s="25"/>
     </row>
-    <row r="225" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="225" spans="2:56" x14ac:dyDescent="0.2">
       <c r="E225" s="165"/>
       <c r="G225"/>
       <c r="H225" s="166"/>
@@ -63369,7 +63369,7 @@
       <c r="BC225" s="12"/>
       <c r="BD225" s="25"/>
     </row>
-    <row r="226" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="226" spans="2:56" x14ac:dyDescent="0.2">
       <c r="C226" s="172" t="s">
         <v>46</v>
       </c>
@@ -63418,7 +63418,7 @@
       <c r="BC226" s="12"/>
       <c r="BD226" s="25"/>
     </row>
-    <row r="227" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="227" spans="2:56" x14ac:dyDescent="0.2">
       <c r="C227" s="172" t="s">
         <v>66</v>
       </c>
@@ -63467,7 +63467,7 @@
       <c r="BC227" s="12"/>
       <c r="BD227" s="25"/>
     </row>
-    <row r="228" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="228" spans="2:56" x14ac:dyDescent="0.2">
       <c r="C228" s="172"/>
       <c r="D228"/>
       <c r="G228" s="172"/>
@@ -63514,7 +63514,7 @@
       <c r="BC228" s="12"/>
       <c r="BD228" s="25"/>
     </row>
-    <row r="229" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="229" spans="2:56" x14ac:dyDescent="0.2">
       <c r="C229" s="172" t="s">
         <v>67</v>
       </c>
@@ -63563,7 +63563,7 @@
       <c r="BC229" s="12"/>
       <c r="BD229" s="25"/>
     </row>
-    <row r="230" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="230" spans="2:56" x14ac:dyDescent="0.2">
       <c r="C230" s="172" t="s">
         <v>68</v>
       </c>
@@ -63611,7 +63611,7 @@
       <c r="BC230" s="12"/>
       <c r="BD230" s="25"/>
     </row>
-    <row r="231" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="231" spans="2:56" x14ac:dyDescent="0.2">
       <c r="C231" s="24"/>
       <c r="D231"/>
       <c r="G231" s="172"/>
@@ -63657,7 +63657,7 @@
       <c r="BC231" s="12"/>
       <c r="BD231" s="25"/>
     </row>
-    <row r="232" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="232" spans="2:56" x14ac:dyDescent="0.2">
       <c r="B232" s="6"/>
       <c r="C232" s="172" t="s">
         <v>69</v>
@@ -63706,7 +63706,7 @@
       <c r="BC232" s="12"/>
       <c r="BD232" s="25"/>
     </row>
-    <row r="233" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="233" spans="2:56" x14ac:dyDescent="0.2">
       <c r="C233" s="172"/>
       <c r="D233" s="24"/>
       <c r="G233" s="172"/>
@@ -63749,7 +63749,7 @@
       <c r="BC233" s="12"/>
       <c r="BD233" s="25"/>
     </row>
-    <row r="234" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="234" spans="2:56" x14ac:dyDescent="0.2">
       <c r="C234" s="172"/>
       <c r="D234" s="24"/>
       <c r="G234" s="172"/>
@@ -63792,7 +63792,7 @@
       <c r="BC234" s="12"/>
       <c r="BD234" s="25"/>
     </row>
-    <row r="235" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="235" spans="2:56" x14ac:dyDescent="0.2">
       <c r="B235" s="10" t="s">
         <v>70</v>
       </c>
@@ -63838,7 +63838,7 @@
       <c r="BC235" s="12"/>
       <c r="BD235" s="25"/>
     </row>
-    <row r="236" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="236" spans="2:56" x14ac:dyDescent="0.2">
       <c r="C236" s="172"/>
       <c r="D236" s="24"/>
       <c r="F236" s="172"/>
@@ -63881,7 +63881,7 @@
       <c r="BC236" s="12"/>
       <c r="BD236" s="25"/>
     </row>
-    <row r="237" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="237" spans="2:56" x14ac:dyDescent="0.2">
       <c r="C237" s="24">
         <v>1</v>
       </c>
@@ -63929,7 +63929,7 @@
       <c r="AS237"/>
       <c r="AT237"/>
     </row>
-    <row r="238" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="238" spans="2:56" x14ac:dyDescent="0.2">
       <c r="C238"/>
       <c r="D238" s="24" t="s">
         <v>73</v>
@@ -63974,7 +63974,7 @@
       <c r="AS238"/>
       <c r="AT238"/>
     </row>
-    <row r="239" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="239" spans="2:56" x14ac:dyDescent="0.2">
       <c r="C239"/>
       <c r="D239" s="24" t="s">
         <v>18</v>
@@ -64019,7 +64019,7 @@
       <c r="AS239"/>
       <c r="AT239"/>
     </row>
-    <row r="240" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="240" spans="2:56" x14ac:dyDescent="0.2">
       <c r="C240"/>
       <c r="D240"/>
       <c r="E240" s="13" t="s">
@@ -64059,7 +64059,7 @@
       <c r="AS240"/>
       <c r="AT240"/>
     </row>
-    <row r="241" spans="3:46" x14ac:dyDescent="0.15">
+    <row r="241" spans="3:46" x14ac:dyDescent="0.2">
       <c r="C241"/>
       <c r="D241"/>
       <c r="G241"/>
@@ -64098,11 +64098,34 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="AK6:AO6"/>
-    <mergeCell ref="AK7:AK8"/>
-    <mergeCell ref="AM7:AM8"/>
-    <mergeCell ref="AN7:AN8"/>
-    <mergeCell ref="AO7:AO8"/>
+    <mergeCell ref="AP6:AT6"/>
+    <mergeCell ref="AP7:AP8"/>
+    <mergeCell ref="AR7:AR8"/>
+    <mergeCell ref="AS7:AS8"/>
+    <mergeCell ref="AT7:AT8"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:F8"/>
+    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="H6:K6"/>
+    <mergeCell ref="L6:N6"/>
+    <mergeCell ref="O6:P6"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="H7:H8"/>
+    <mergeCell ref="I7:I8"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="Q7:Q8"/>
+    <mergeCell ref="R7:R8"/>
+    <mergeCell ref="AF6:AJ6"/>
+    <mergeCell ref="AF7:AF8"/>
+    <mergeCell ref="AH7:AH8"/>
+    <mergeCell ref="AI7:AI8"/>
+    <mergeCell ref="AJ7:AJ8"/>
     <mergeCell ref="AC7:AC8"/>
     <mergeCell ref="AD7:AD8"/>
     <mergeCell ref="AE7:AE8"/>
@@ -64117,34 +64140,11 @@
     <mergeCell ref="AA6:AE6"/>
     <mergeCell ref="AA7:AA8"/>
     <mergeCell ref="S6:T6"/>
-    <mergeCell ref="AF6:AJ6"/>
-    <mergeCell ref="AF7:AF8"/>
-    <mergeCell ref="AH7:AH8"/>
-    <mergeCell ref="AI7:AI8"/>
-    <mergeCell ref="AJ7:AJ8"/>
-    <mergeCell ref="H6:K6"/>
-    <mergeCell ref="L6:N6"/>
-    <mergeCell ref="O6:P6"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="H7:H8"/>
-    <mergeCell ref="I7:I8"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="Q7:Q8"/>
-    <mergeCell ref="R7:R8"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:F8"/>
-    <mergeCell ref="G6:G8"/>
-    <mergeCell ref="AP6:AT6"/>
-    <mergeCell ref="AP7:AP8"/>
-    <mergeCell ref="AR7:AR8"/>
-    <mergeCell ref="AS7:AS8"/>
-    <mergeCell ref="AT7:AT8"/>
+    <mergeCell ref="AK6:AO6"/>
+    <mergeCell ref="AK7:AK8"/>
+    <mergeCell ref="AM7:AM8"/>
+    <mergeCell ref="AN7:AN8"/>
+    <mergeCell ref="AO7:AO8"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0" top="0.27559055118110237" bottom="0.27559055118110237" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="57" orientation="landscape" horizontalDpi="4294967293" r:id="rId1"/>
@@ -64154,52 +64154,52 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:BH100"/>
-  <sheetFormatPr defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.83203125" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" style="179" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.6640625" style="23" customWidth="1"/>
-    <col min="5" max="5" width="2.83203125" customWidth="1"/>
-    <col min="6" max="6" width="35.1640625" customWidth="1"/>
+    <col min="1" max="1" width="2.85546875" customWidth="1"/>
+    <col min="3" max="3" width="14.7109375" style="179" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.7109375" style="23" customWidth="1"/>
+    <col min="5" max="5" width="2.85546875" customWidth="1"/>
+    <col min="6" max="6" width="35.140625" customWidth="1"/>
     <col min="7" max="7" width="14" style="24" customWidth="1"/>
-    <col min="8" max="8" width="17.5" style="25" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" style="25" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="15.6640625" style="25" hidden="1" customWidth="1"/>
-    <col min="11" max="13" width="18.5" style="25" hidden="1" customWidth="1"/>
-    <col min="14" max="14" width="14.1640625" style="25" customWidth="1"/>
-    <col min="15" max="16" width="7.83203125" customWidth="1"/>
-    <col min="17" max="17" width="8.33203125" customWidth="1"/>
-    <col min="18" max="20" width="7.83203125" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" style="25" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="16.85546875" style="25" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="15.7109375" style="25" hidden="1" customWidth="1"/>
+    <col min="11" max="13" width="18.42578125" style="25" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="14.140625" style="25" customWidth="1"/>
+    <col min="15" max="16" width="7.85546875" customWidth="1"/>
+    <col min="17" max="17" width="8.28515625" customWidth="1"/>
+    <col min="18" max="20" width="7.85546875" customWidth="1"/>
     <col min="21" max="21" width="15" customWidth="1"/>
     <col min="22" max="22" width="8" customWidth="1"/>
-    <col min="23" max="23" width="7.1640625" customWidth="1"/>
-    <col min="24" max="25" width="15.83203125" customWidth="1"/>
-    <col min="26" max="26" width="18.1640625" customWidth="1"/>
-    <col min="27" max="28" width="8.1640625" customWidth="1"/>
-    <col min="29" max="29" width="13.5" customWidth="1"/>
-    <col min="30" max="30" width="14.1640625" customWidth="1"/>
+    <col min="23" max="23" width="7.140625" customWidth="1"/>
+    <col min="24" max="25" width="15.85546875" customWidth="1"/>
+    <col min="26" max="26" width="18.140625" customWidth="1"/>
+    <col min="27" max="28" width="8.140625" customWidth="1"/>
+    <col min="29" max="29" width="13.42578125" customWidth="1"/>
+    <col min="30" max="30" width="14.140625" customWidth="1"/>
     <col min="31" max="31" width="15" customWidth="1"/>
-    <col min="32" max="32" width="8.33203125" customWidth="1"/>
-    <col min="33" max="33" width="7.83203125" customWidth="1"/>
-    <col min="34" max="34" width="16.5" customWidth="1"/>
-    <col min="35" max="35" width="15.83203125" customWidth="1"/>
-    <col min="36" max="36" width="15.33203125" customWidth="1"/>
+    <col min="32" max="32" width="8.28515625" customWidth="1"/>
+    <col min="33" max="33" width="7.85546875" customWidth="1"/>
+    <col min="34" max="34" width="16.42578125" customWidth="1"/>
+    <col min="35" max="35" width="15.85546875" customWidth="1"/>
+    <col min="36" max="36" width="15.28515625" customWidth="1"/>
     <col min="37" max="38" width="9" customWidth="1"/>
-    <col min="39" max="39" width="14.5" customWidth="1"/>
-    <col min="40" max="40" width="15.6640625" customWidth="1"/>
-    <col min="41" max="41" width="16.5" customWidth="1"/>
-    <col min="42" max="42" width="8.6640625" customWidth="1"/>
-    <col min="43" max="43" width="8.5" customWidth="1"/>
-    <col min="44" max="46" width="16.5" customWidth="1"/>
-    <col min="47" max="47" width="1.5" customWidth="1"/>
+    <col min="39" max="39" width="14.42578125" customWidth="1"/>
+    <col min="40" max="40" width="15.7109375" customWidth="1"/>
+    <col min="41" max="41" width="16.42578125" customWidth="1"/>
+    <col min="42" max="42" width="8.7109375" customWidth="1"/>
+    <col min="43" max="43" width="8.42578125" customWidth="1"/>
+    <col min="44" max="46" width="16.42578125" customWidth="1"/>
+    <col min="47" max="47" width="1.42578125" customWidth="1"/>
     <col min="48" max="48" width="14" customWidth="1"/>
-    <col min="49" max="60" width="12.83203125" customWidth="1"/>
-    <col min="61" max="61" width="2.5" customWidth="1"/>
-    <col min="62" max="62" width="12.1640625" customWidth="1"/>
+    <col min="49" max="60" width="12.85546875" customWidth="1"/>
+    <col min="61" max="61" width="2.42578125" customWidth="1"/>
+    <col min="62" max="62" width="12.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:60" ht="11.25" thickBot="1" x14ac:dyDescent="0.2"/>
-    <row r="2" spans="2:60" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="2:60" ht="10.8" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:60" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="14" t="s">
         <v>293</v>
       </c>
@@ -64232,7 +64232,7 @@
       <c r="X2" s="2"/>
       <c r="Y2" s="2"/>
     </row>
-    <row r="3" spans="2:60" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="2:60" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
         <v>23</v>
       </c>
@@ -64264,7 +64264,7 @@
       <c r="X3" s="34"/>
       <c r="Y3" s="34"/>
     </row>
-    <row r="4" spans="2:60" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:60" ht="11.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B4" s="4" t="s">
         <v>24</v>
       </c>
@@ -64296,7 +64296,7 @@
       <c r="X4" s="2"/>
       <c r="Y4" s="2"/>
     </row>
-    <row r="6" spans="2:60" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" spans="2:60" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B6" s="391" t="s">
         <v>7</v>
       </c>
@@ -64306,34 +64306,34 @@
       <c r="D6" s="444" t="s">
         <v>111</v>
       </c>
-      <c r="E6" s="399" t="s">
+      <c r="E6" s="403" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="400"/>
+      <c r="F6" s="404"/>
       <c r="G6" s="431" t="s">
         <v>31</v>
       </c>
-      <c r="H6" s="409" t="s">
+      <c r="H6" s="413" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="409"/>
-      <c r="J6" s="409"/>
-      <c r="K6" s="409"/>
-      <c r="L6" s="414"/>
-      <c r="M6" s="415"/>
-      <c r="N6" s="416"/>
-      <c r="O6" s="417" t="s">
+      <c r="I6" s="413"/>
+      <c r="J6" s="413"/>
+      <c r="K6" s="413"/>
+      <c r="L6" s="418"/>
+      <c r="M6" s="419"/>
+      <c r="N6" s="420"/>
+      <c r="O6" s="421" t="s">
         <v>33</v>
       </c>
-      <c r="P6" s="419"/>
-      <c r="Q6" s="420" t="s">
+      <c r="P6" s="423"/>
+      <c r="Q6" s="396" t="s">
         <v>34</v>
       </c>
-      <c r="R6" s="421"/>
-      <c r="S6" s="420" t="s">
+      <c r="R6" s="397"/>
+      <c r="S6" s="396" t="s">
         <v>35</v>
       </c>
-      <c r="T6" s="421"/>
+      <c r="T6" s="397"/>
       <c r="U6" s="392" t="s">
         <v>36</v>
       </c>
@@ -64374,51 +64374,51 @@
       <c r="AT6" s="390"/>
       <c r="AU6" s="283"/>
     </row>
-    <row r="7" spans="2:60" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" spans="2:60" s="6" customFormat="1" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="391"/>
       <c r="C7" s="430"/>
       <c r="D7" s="445"/>
-      <c r="E7" s="401"/>
-      <c r="F7" s="402"/>
+      <c r="E7" s="405"/>
+      <c r="F7" s="406"/>
       <c r="G7" s="432"/>
-      <c r="H7" s="410">
+      <c r="H7" s="414">
         <v>43100</v>
       </c>
-      <c r="I7" s="411" t="s">
+      <c r="I7" s="415" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="411" t="s">
+      <c r="J7" s="415" t="s">
         <v>39</v>
       </c>
       <c r="K7" s="44">
         <v>43465</v>
       </c>
-      <c r="L7" s="411" t="s">
+      <c r="L7" s="415" t="s">
         <v>8</v>
       </c>
-      <c r="M7" s="411" t="s">
+      <c r="M7" s="415" t="s">
         <v>9</v>
       </c>
       <c r="N7" s="44">
         <f>K7</f>
         <v>43465</v>
       </c>
-      <c r="O7" s="422" t="s">
+      <c r="O7" s="394" t="s">
         <v>43</v>
       </c>
-      <c r="P7" s="422" t="s">
+      <c r="P7" s="394" t="s">
         <v>42</v>
       </c>
-      <c r="Q7" s="422" t="s">
+      <c r="Q7" s="394" t="s">
         <v>42</v>
       </c>
-      <c r="R7" s="422" t="s">
+      <c r="R7" s="394" t="s">
         <v>43</v>
       </c>
-      <c r="S7" s="422" t="s">
+      <c r="S7" s="394" t="s">
         <v>42</v>
       </c>
-      <c r="T7" s="422" t="s">
+      <c r="T7" s="394" t="s">
         <v>43</v>
       </c>
       <c r="U7" s="392"/>
@@ -64528,30 +64528,30 @@
         <v>271</v>
       </c>
     </row>
-    <row r="8" spans="2:60" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="8" spans="2:60" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B8" s="391"/>
       <c r="C8" s="430"/>
       <c r="D8" s="446"/>
-      <c r="E8" s="403"/>
-      <c r="F8" s="404"/>
+      <c r="E8" s="407"/>
+      <c r="F8" s="408"/>
       <c r="G8" s="433"/>
-      <c r="H8" s="411"/>
-      <c r="I8" s="411"/>
-      <c r="J8" s="411"/>
+      <c r="H8" s="415"/>
+      <c r="I8" s="415"/>
+      <c r="J8" s="415"/>
       <c r="K8" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="L8" s="411"/>
-      <c r="M8" s="411"/>
+      <c r="L8" s="415"/>
+      <c r="M8" s="415"/>
       <c r="N8" s="48" t="s">
         <v>11</v>
       </c>
-      <c r="O8" s="423"/>
-      <c r="P8" s="423"/>
-      <c r="Q8" s="423"/>
-      <c r="R8" s="423"/>
-      <c r="S8" s="423"/>
-      <c r="T8" s="423"/>
+      <c r="O8" s="395"/>
+      <c r="P8" s="395"/>
+      <c r="Q8" s="395"/>
+      <c r="R8" s="395"/>
+      <c r="S8" s="395"/>
+      <c r="T8" s="395"/>
       <c r="U8" s="392"/>
       <c r="V8" s="391"/>
       <c r="W8" s="275"/>
@@ -64595,7 +64595,7 @@
       <c r="BG8" s="199"/>
       <c r="BH8" s="199"/>
     </row>
-    <row r="9" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="9" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B9" s="52"/>
       <c r="C9" s="183"/>
       <c r="D9" s="54"/>
@@ -64642,7 +64642,7 @@
       <c r="AS9" s="367"/>
       <c r="AT9" s="367"/>
     </row>
-    <row r="10" spans="2:60" s="6" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="10" spans="2:60" s="6" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B10" s="61"/>
       <c r="C10" s="184" t="s">
         <v>15</v>
@@ -64692,7 +64692,7 @@
       <c r="AT10" s="284"/>
       <c r="AU10" s="284"/>
     </row>
-    <row r="11" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="11" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B11" s="68"/>
       <c r="C11" s="89"/>
       <c r="D11" s="70"/>
@@ -64739,7 +64739,7 @@
       <c r="AS11" s="367"/>
       <c r="AT11" s="367"/>
     </row>
-    <row r="12" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="12" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B12" s="68"/>
       <c r="C12" s="89">
         <v>40792</v>
@@ -64918,7 +64918,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="13" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B13" s="68"/>
       <c r="C13" s="89">
         <v>40843</v>
@@ -65097,7 +65097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="14" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B14" s="68"/>
       <c r="C14" s="89">
         <v>41351</v>
@@ -65276,7 +65276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="15" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B15" s="68"/>
       <c r="C15" s="89">
         <v>41572</v>
@@ -65455,7 +65455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="16" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B16" s="68"/>
       <c r="C16" s="89">
         <v>42013</v>
@@ -65644,7 +65644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B17" s="68"/>
       <c r="C17" s="89">
         <v>42146</v>
@@ -65839,7 +65839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B18" s="68"/>
       <c r="C18" s="89">
         <v>42252</v>
@@ -66034,7 +66034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B19" s="68"/>
       <c r="C19" s="89">
         <v>42510</v>
@@ -66241,7 +66241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B20" s="68"/>
       <c r="C20" s="89">
         <v>42515</v>
@@ -66448,7 +66448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B21" s="68"/>
       <c r="C21" s="89">
         <v>42812</v>
@@ -66657,7 +66657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B22" s="97"/>
       <c r="C22" s="257">
         <v>43207</v>
@@ -66863,7 +66863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B23" s="97"/>
       <c r="C23" s="257"/>
       <c r="D23" s="258"/>
@@ -66924,7 +66924,7 @@
       <c r="BG23" s="172"/>
       <c r="BH23" s="172"/>
     </row>
-    <row r="24" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B24" s="97"/>
       <c r="C24" s="257">
         <v>43749</v>
@@ -67127,7 +67127,7 @@
         <v>19270.833333333332</v>
       </c>
     </row>
-    <row r="25" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B25" s="97"/>
       <c r="C25" s="257">
         <v>43769</v>
@@ -67330,7 +67330,7 @@
         <v>258522.72916666666</v>
       </c>
     </row>
-    <row r="26" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B26" s="97"/>
       <c r="C26" s="257"/>
       <c r="D26" s="258"/>
@@ -67378,7 +67378,7 @@
       <c r="AT26" s="110"/>
       <c r="AU26" s="285"/>
     </row>
-    <row r="27" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B27" s="97"/>
       <c r="C27" s="257">
         <v>43902</v>
@@ -67577,7 +67577,7 @@
         <v>20833.333333333332</v>
       </c>
     </row>
-    <row r="28" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B28" s="97"/>
       <c r="C28" s="98"/>
       <c r="D28" s="99"/>
@@ -67625,7 +67625,7 @@
       <c r="AT28" s="222"/>
       <c r="AU28" s="285"/>
     </row>
-    <row r="29" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B29" s="97"/>
       <c r="C29" s="98"/>
       <c r="D29" s="99"/>
@@ -67776,7 +67776,7 @@
         <v>298626.89583333331</v>
       </c>
     </row>
-    <row r="30" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B30" s="97"/>
       <c r="C30" s="98"/>
       <c r="D30" s="99"/>
@@ -67824,7 +67824,7 @@
       <c r="AT30" s="232"/>
       <c r="AU30" s="285"/>
     </row>
-    <row r="31" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B31" s="97"/>
       <c r="C31" s="257">
         <v>44365</v>
@@ -68025,7 +68025,7 @@
         <v>52406.25</v>
       </c>
     </row>
-    <row r="32" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B32" s="97"/>
       <c r="C32" s="257">
         <v>44365</v>
@@ -68226,7 +68226,7 @@
         <v>29437.5</v>
       </c>
     </row>
-    <row r="33" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B33" s="97"/>
       <c r="C33" s="257">
         <v>44365</v>
@@ -68427,7 +68427,7 @@
         <v>58125</v>
       </c>
     </row>
-    <row r="34" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B34" s="97"/>
       <c r="C34" s="257">
         <v>44365</v>
@@ -68628,7 +68628,7 @@
         <v>23906.25</v>
       </c>
     </row>
-    <row r="35" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B35" s="97"/>
       <c r="C35" s="257">
         <v>44365</v>
@@ -68829,7 +68829,7 @@
         <v>71484.375</v>
       </c>
     </row>
-    <row r="36" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B36" s="97"/>
       <c r="C36" s="257">
         <v>44365</v>
@@ -69030,7 +69030,7 @@
         <v>171093.75</v>
       </c>
     </row>
-    <row r="37" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B37" s="97"/>
       <c r="C37" s="257">
         <v>44365</v>
@@ -69231,7 +69231,7 @@
         <v>46125</v>
       </c>
     </row>
-    <row r="38" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B38" s="97"/>
       <c r="C38" s="257">
         <v>44365</v>
@@ -69432,7 +69432,7 @@
         <v>77884.375</v>
       </c>
     </row>
-    <row r="39" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B39" s="97"/>
       <c r="C39" s="257">
         <v>44380</v>
@@ -69633,7 +69633,7 @@
         <v>9895.8333333333339</v>
       </c>
     </row>
-    <row r="40" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B40" s="97"/>
       <c r="C40" s="257">
         <v>44390</v>
@@ -69834,7 +69834,7 @@
         <v>47916.666666666664</v>
       </c>
     </row>
-    <row r="41" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B41" s="97"/>
       <c r="C41" s="257">
         <v>44496</v>
@@ -70035,7 +70035,7 @@
         <v>31562.5</v>
       </c>
     </row>
-    <row r="42" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="42" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B42" s="97"/>
       <c r="C42" s="257">
         <v>44497</v>
@@ -70236,7 +70236,7 @@
         <v>364583.33333333331</v>
       </c>
     </row>
-    <row r="43" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B43" s="97"/>
       <c r="C43" s="257"/>
       <c r="D43" s="273"/>
@@ -70284,7 +70284,7 @@
       <c r="AT43" s="232"/>
       <c r="AU43" s="285"/>
     </row>
-    <row r="44" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="44" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B44" s="97"/>
       <c r="C44" s="98"/>
       <c r="D44" s="99"/>
@@ -70435,7 +70435,7 @@
         <v>984420.83333333326</v>
       </c>
     </row>
-    <row r="45" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="45" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B45" s="97"/>
       <c r="C45" s="98"/>
       <c r="D45" s="99"/>
@@ -70496,7 +70496,7 @@
       <c r="BG45" s="255"/>
       <c r="BH45" s="255"/>
     </row>
-    <row r="46" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="46" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B46" s="97"/>
       <c r="C46" s="257">
         <v>44721</v>
@@ -70697,7 +70697,7 @@
         <v>179625</v>
       </c>
     </row>
-    <row r="47" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="47" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B47" s="97"/>
       <c r="C47" s="257">
         <v>44816</v>
@@ -70898,7 +70898,7 @@
         <v>23958.333333333332</v>
       </c>
     </row>
-    <row r="48" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="48" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B48" s="97"/>
       <c r="C48" s="257">
         <v>44900</v>
@@ -71099,7 +71099,7 @@
         <v>26041.666666666668</v>
       </c>
     </row>
-    <row r="49" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B49" s="97"/>
       <c r="C49" s="98"/>
       <c r="D49" s="99"/>
@@ -71160,7 +71160,7 @@
       <c r="BG49" s="255"/>
       <c r="BH49" s="255"/>
     </row>
-    <row r="50" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B50" s="97"/>
       <c r="C50" s="98"/>
       <c r="D50" s="99"/>
@@ -71311,7 +71311,7 @@
         <v>229625</v>
       </c>
     </row>
-    <row r="51" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B51" s="97"/>
       <c r="C51" s="98"/>
       <c r="D51" s="99"/>
@@ -71372,7 +71372,7 @@
       <c r="BG51" s="255"/>
       <c r="BH51" s="255"/>
     </row>
-    <row r="52" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B52" s="97"/>
       <c r="C52" s="89">
         <v>44929</v>
@@ -71571,7 +71571,7 @@
         <v>19791.666666666668</v>
       </c>
     </row>
-    <row r="53" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B53" s="97"/>
       <c r="C53" s="89" t="s">
         <v>396</v>
@@ -71771,7 +71771,7 @@
         <v>26562.5</v>
       </c>
     </row>
-    <row r="54" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B54" s="97"/>
       <c r="C54" s="89" t="s">
         <v>401</v>
@@ -71970,7 +71970,7 @@
         <v>11261.261250000001</v>
       </c>
     </row>
-    <row r="55" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B55" s="97"/>
       <c r="C55" s="89">
         <v>45112</v>
@@ -72169,7 +72169,7 @@
         <v>241666.66666666666</v>
       </c>
     </row>
-    <row r="56" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B56" s="97"/>
       <c r="C56" s="89">
         <v>45134</v>
@@ -72368,7 +72368,7 @@
         <v>50520.833333333336</v>
       </c>
     </row>
-    <row r="57" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B57" s="97"/>
       <c r="C57" s="89">
         <v>45210</v>
@@ -72567,7 +72567,7 @@
         <v>10416.666666666666</v>
       </c>
     </row>
-    <row r="58" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B58" s="97"/>
       <c r="C58" s="89"/>
       <c r="D58" s="268"/>
@@ -72628,7 +72628,7 @@
       <c r="BG58" s="255"/>
       <c r="BH58" s="255"/>
     </row>
-    <row r="59" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B59" s="97"/>
       <c r="C59" s="89"/>
       <c r="D59" s="268"/>
@@ -72779,7 +72779,7 @@
         <v>360219.59458333335</v>
       </c>
     </row>
-    <row r="60" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B60" s="97"/>
       <c r="C60" s="89"/>
       <c r="D60" s="268"/>
@@ -72840,7 +72840,7 @@
       <c r="BG60" s="256"/>
       <c r="BH60" s="256"/>
     </row>
-    <row r="61" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B61" s="97"/>
       <c r="C61" s="89">
         <v>45475</v>
@@ -73034,7 +73034,7 @@
         <v>15625</v>
       </c>
     </row>
-    <row r="62" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B62" s="97"/>
       <c r="C62" s="257">
         <v>45540</v>
@@ -73228,7 +73228,7 @@
         <v>9895.8333333333339</v>
       </c>
     </row>
-    <row r="63" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B63" s="97"/>
       <c r="C63" s="89">
         <v>45586</v>
@@ -73422,7 +73422,7 @@
         <v>47916.666666666664</v>
       </c>
     </row>
-    <row r="64" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B64" s="97"/>
       <c r="C64" s="89"/>
       <c r="D64" s="268"/>
@@ -73483,7 +73483,7 @@
       <c r="BG64" s="256"/>
       <c r="BH64" s="256"/>
     </row>
-    <row r="65" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="65" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B65" s="97"/>
       <c r="C65" s="89"/>
       <c r="D65" s="268"/>
@@ -73616,7 +73616,7 @@
         <v>73437.5</v>
       </c>
     </row>
-    <row r="66" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="66" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B66" s="97"/>
       <c r="C66" s="89"/>
       <c r="D66" s="268"/>
@@ -73677,7 +73677,7 @@
       <c r="BG66" s="256"/>
       <c r="BH66" s="256"/>
     </row>
-    <row r="67" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="67" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B67" s="97"/>
       <c r="C67" s="89"/>
       <c r="D67" s="268"/>
@@ -73738,7 +73738,7 @@
       <c r="BG67" s="256"/>
       <c r="BH67" s="256"/>
     </row>
-    <row r="68" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="68" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B68" s="97"/>
       <c r="C68" s="89"/>
       <c r="D68" s="268"/>
@@ -73799,7 +73799,7 @@
       <c r="BG68" s="256"/>
       <c r="BH68" s="256"/>
     </row>
-    <row r="69" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="69" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B69" s="97"/>
       <c r="C69" s="89"/>
       <c r="D69" s="268"/>
@@ -73860,7 +73860,7 @@
       <c r="BG69" s="256"/>
       <c r="BH69" s="256"/>
     </row>
-    <row r="70" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="70" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B70" s="97"/>
       <c r="C70" s="89"/>
       <c r="D70" s="268"/>
@@ -73921,7 +73921,7 @@
       <c r="BG70" s="256"/>
       <c r="BH70" s="256"/>
     </row>
-    <row r="71" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="71" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B71" s="97"/>
       <c r="C71" s="98"/>
       <c r="D71" s="99"/>
@@ -74075,7 +74075,7 @@
         <v>1946329.82375</v>
       </c>
     </row>
-    <row r="72" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="72" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B72" s="97"/>
       <c r="C72" s="98"/>
       <c r="D72" s="99"/>
@@ -74136,7 +74136,7 @@
       <c r="BG72" s="297"/>
       <c r="BH72" s="297"/>
     </row>
-    <row r="73" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="73" spans="2:60" s="11" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B73" s="97"/>
       <c r="C73" s="98"/>
       <c r="D73" s="99"/>
@@ -74197,7 +74197,7 @@
       <c r="BG73" s="297"/>
       <c r="BH73" s="297"/>
     </row>
-    <row r="74" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="74" spans="2:60" x14ac:dyDescent="0.2">
       <c r="E74" s="165"/>
       <c r="F74" t="s">
         <v>259</v>
@@ -74209,7 +74209,7 @@
       <c r="T74" s="170"/>
       <c r="U74" s="172"/>
     </row>
-    <row r="75" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="75" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B75" s="10"/>
       <c r="C75" s="23"/>
       <c r="E75" s="165"/>
@@ -74230,7 +74230,7 @@
       <c r="BC75" s="12"/>
       <c r="BD75" s="25"/>
     </row>
-    <row r="76" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="76" spans="2:60" x14ac:dyDescent="0.2">
       <c r="B76" s="10"/>
       <c r="C76" s="23"/>
       <c r="E76" s="165"/>
@@ -74251,7 +74251,7 @@
       <c r="BC76" s="12"/>
       <c r="BD76" s="25"/>
     </row>
-    <row r="77" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="77" spans="2:60" x14ac:dyDescent="0.2">
       <c r="C77" s="173"/>
       <c r="E77" s="165"/>
       <c r="G77"/>
@@ -74271,7 +74271,7 @@
       <c r="BC77" s="12"/>
       <c r="BD77" s="25"/>
     </row>
-    <row r="78" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="78" spans="2:60" x14ac:dyDescent="0.2">
       <c r="C78" s="172"/>
       <c r="E78" s="165"/>
       <c r="G78"/>
@@ -74294,7 +74294,7 @@
       <c r="BC78" s="12"/>
       <c r="BD78" s="25"/>
     </row>
-    <row r="79" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="79" spans="2:60" x14ac:dyDescent="0.2">
       <c r="C79" s="172"/>
       <c r="E79" s="165"/>
       <c r="G79"/>
@@ -74317,7 +74317,7 @@
       <c r="BC79" s="12"/>
       <c r="BD79" s="25"/>
     </row>
-    <row r="80" spans="2:60" x14ac:dyDescent="0.15">
+    <row r="80" spans="2:60" x14ac:dyDescent="0.2">
       <c r="C80" s="172"/>
       <c r="E80" s="165"/>
       <c r="G80"/>
@@ -74340,7 +74340,7 @@
       <c r="BC80" s="12"/>
       <c r="BD80" s="25"/>
     </row>
-    <row r="81" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="81" spans="2:56" x14ac:dyDescent="0.2">
       <c r="C81" s="23"/>
       <c r="E81" s="165"/>
       <c r="G81"/>
@@ -74360,7 +74360,7 @@
       <c r="BC81" s="12"/>
       <c r="BD81" s="25"/>
     </row>
-    <row r="82" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="82" spans="2:56" x14ac:dyDescent="0.2">
       <c r="C82" s="23"/>
       <c r="E82" s="165"/>
       <c r="G82"/>
@@ -74380,7 +74380,7 @@
       <c r="BC82" s="12"/>
       <c r="BD82" s="25"/>
     </row>
-    <row r="83" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="83" spans="2:56" x14ac:dyDescent="0.2">
       <c r="C83" s="173"/>
       <c r="E83" s="165"/>
       <c r="G83"/>
@@ -74400,7 +74400,7 @@
       <c r="BC83" s="12"/>
       <c r="BD83" s="25"/>
     </row>
-    <row r="84" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="84" spans="2:56" x14ac:dyDescent="0.2">
       <c r="C84" s="23"/>
       <c r="E84" s="165"/>
       <c r="G84"/>
@@ -74420,7 +74420,7 @@
       <c r="BC84" s="12"/>
       <c r="BD84" s="25"/>
     </row>
-    <row r="85" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="85" spans="2:56" x14ac:dyDescent="0.2">
       <c r="C85" s="172"/>
       <c r="D85"/>
       <c r="G85" s="172"/>
@@ -74445,7 +74445,7 @@
       <c r="BC85" s="12"/>
       <c r="BD85" s="25"/>
     </row>
-    <row r="86" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="86" spans="2:56" x14ac:dyDescent="0.2">
       <c r="C86" s="172"/>
       <c r="D86"/>
       <c r="G86" s="172"/>
@@ -74470,7 +74470,7 @@
       <c r="BC86" s="12"/>
       <c r="BD86" s="25"/>
     </row>
-    <row r="87" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="87" spans="2:56" x14ac:dyDescent="0.2">
       <c r="C87" s="172"/>
       <c r="D87"/>
       <c r="G87" s="172"/>
@@ -74495,7 +74495,7 @@
       <c r="BC87" s="12"/>
       <c r="BD87" s="25"/>
     </row>
-    <row r="88" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="88" spans="2:56" x14ac:dyDescent="0.2">
       <c r="C88" s="172"/>
       <c r="D88"/>
       <c r="G88" s="172"/>
@@ -74517,7 +74517,7 @@
       <c r="BC88" s="12"/>
       <c r="BD88" s="25"/>
     </row>
-    <row r="89" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="89" spans="2:56" x14ac:dyDescent="0.2">
       <c r="C89" s="172"/>
       <c r="D89"/>
       <c r="G89" s="172"/>
@@ -74538,7 +74538,7 @@
       <c r="BC89" s="12"/>
       <c r="BD89" s="25"/>
     </row>
-    <row r="90" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="90" spans="2:56" x14ac:dyDescent="0.2">
       <c r="C90" s="24"/>
       <c r="D90"/>
       <c r="G90" s="172"/>
@@ -74562,7 +74562,7 @@
       <c r="BC90" s="12"/>
       <c r="BD90" s="25"/>
     </row>
-    <row r="91" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="91" spans="2:56" x14ac:dyDescent="0.2">
       <c r="B91" s="6"/>
       <c r="C91" s="172"/>
       <c r="D91"/>
@@ -74587,7 +74587,7 @@
       <c r="BC91" s="12"/>
       <c r="BD91" s="25"/>
     </row>
-    <row r="92" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="92" spans="2:56" x14ac:dyDescent="0.2">
       <c r="C92" s="172"/>
       <c r="D92" s="24"/>
       <c r="G92" s="172"/>
@@ -74608,7 +74608,7 @@
       <c r="BC92" s="12"/>
       <c r="BD92" s="25"/>
     </row>
-    <row r="93" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="93" spans="2:56" x14ac:dyDescent="0.2">
       <c r="C93" s="172"/>
       <c r="D93" s="24"/>
       <c r="G93" s="172"/>
@@ -74629,7 +74629,7 @@
       <c r="BC93" s="12"/>
       <c r="BD93" s="25"/>
     </row>
-    <row r="94" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="94" spans="2:56" x14ac:dyDescent="0.2">
       <c r="B94" s="10"/>
       <c r="C94" s="172"/>
       <c r="D94" s="24"/>
@@ -74651,7 +74651,7 @@
       <c r="BC94" s="12"/>
       <c r="BD94" s="25"/>
     </row>
-    <row r="95" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="95" spans="2:56" x14ac:dyDescent="0.2">
       <c r="C95" s="172"/>
       <c r="D95" s="24"/>
       <c r="F95" s="172"/>
@@ -74672,7 +74672,7 @@
       <c r="BC95" s="12"/>
       <c r="BD95" s="25"/>
     </row>
-    <row r="96" spans="2:56" x14ac:dyDescent="0.15">
+    <row r="96" spans="2:56" x14ac:dyDescent="0.2">
       <c r="C96" s="24"/>
       <c r="D96" s="174"/>
       <c r="F96" s="172"/>
@@ -74685,7 +74685,7 @@
       <c r="M96"/>
       <c r="N96"/>
     </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.15">
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97"/>
       <c r="D97" s="24"/>
       <c r="G97" s="172"/>
@@ -74697,7 +74697,7 @@
       <c r="M97"/>
       <c r="N97"/>
     </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.15">
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98"/>
       <c r="D98" s="24"/>
       <c r="F98" s="17"/>
@@ -74713,7 +74713,7 @@
       <c r="M98"/>
       <c r="N98"/>
     </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.15">
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99"/>
       <c r="D99"/>
       <c r="E99" s="13"/>
@@ -74726,7 +74726,7 @@
       <c r="M99"/>
       <c r="N99"/>
     </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.15">
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100"/>
       <c r="D100"/>
       <c r="G100"/>
@@ -74740,32 +74740,11 @@
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="AK6:AO6"/>
-    <mergeCell ref="AK7:AK8"/>
-    <mergeCell ref="AM7:AM8"/>
-    <mergeCell ref="AN7:AN8"/>
-    <mergeCell ref="AO7:AO8"/>
-    <mergeCell ref="AF6:AJ6"/>
-    <mergeCell ref="AF7:AF8"/>
-    <mergeCell ref="AJ7:AJ8"/>
-    <mergeCell ref="AA6:AE6"/>
-    <mergeCell ref="AA7:AA8"/>
-    <mergeCell ref="AC7:AC8"/>
-    <mergeCell ref="AD7:AD8"/>
-    <mergeCell ref="AE7:AE8"/>
-    <mergeCell ref="AH7:AH8"/>
-    <mergeCell ref="AI7:AI8"/>
-    <mergeCell ref="S7:S8"/>
-    <mergeCell ref="T7:T8"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="B6:B8"/>
-    <mergeCell ref="C6:C8"/>
-    <mergeCell ref="D6:D8"/>
-    <mergeCell ref="E6:F8"/>
-    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="AP6:AT6"/>
+    <mergeCell ref="AP7:AP8"/>
+    <mergeCell ref="AR7:AR8"/>
+    <mergeCell ref="AS7:AS8"/>
+    <mergeCell ref="AT7:AT8"/>
     <mergeCell ref="U6:U8"/>
     <mergeCell ref="H7:H8"/>
     <mergeCell ref="I7:I8"/>
@@ -74782,11 +74761,32 @@
     <mergeCell ref="S6:T6"/>
     <mergeCell ref="Q7:Q8"/>
     <mergeCell ref="R7:R8"/>
-    <mergeCell ref="AP6:AT6"/>
-    <mergeCell ref="AP7:AP8"/>
-    <mergeCell ref="AR7:AR8"/>
-    <mergeCell ref="AS7:AS8"/>
-    <mergeCell ref="AT7:AT8"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="C6:C8"/>
+    <mergeCell ref="D6:D8"/>
+    <mergeCell ref="E6:F8"/>
+    <mergeCell ref="G6:G8"/>
+    <mergeCell ref="S7:S8"/>
+    <mergeCell ref="T7:T8"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="P7:P8"/>
+    <mergeCell ref="AF6:AJ6"/>
+    <mergeCell ref="AF7:AF8"/>
+    <mergeCell ref="AJ7:AJ8"/>
+    <mergeCell ref="AA6:AE6"/>
+    <mergeCell ref="AA7:AA8"/>
+    <mergeCell ref="AC7:AC8"/>
+    <mergeCell ref="AD7:AD8"/>
+    <mergeCell ref="AE7:AE8"/>
+    <mergeCell ref="AH7:AH8"/>
+    <mergeCell ref="AI7:AI8"/>
+    <mergeCell ref="AK6:AO6"/>
+    <mergeCell ref="AK7:AK8"/>
+    <mergeCell ref="AM7:AM8"/>
+    <mergeCell ref="AN7:AN8"/>
+    <mergeCell ref="AO7:AO8"/>
   </mergeCells>
   <pageMargins left="0.9055118110236221" right="0" top="0.31496062992125984" bottom="0.31496062992125984" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="58" orientation="landscape" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
@@ -74799,41 +74799,41 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A2:Q30"/>
-  <sheetFormatPr defaultRowHeight="10.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="10.199999999999999" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" customWidth="1"/>
+    <col min="2" max="2" width="9.140625" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="7.6640625" customWidth="1"/>
-    <col min="5" max="5" width="18.1640625" customWidth="1"/>
-    <col min="6" max="6" width="14.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" customWidth="1"/>
-    <col min="8" max="8" width="17.83203125" customWidth="1"/>
+    <col min="4" max="4" width="7.7109375" customWidth="1"/>
+    <col min="5" max="5" width="18.140625" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="8" max="8" width="17.85546875" customWidth="1"/>
     <col min="9" max="9" width="17" customWidth="1"/>
-    <col min="10" max="10" width="17.33203125" customWidth="1"/>
-    <col min="11" max="11" width="13.33203125" customWidth="1"/>
-    <col min="12" max="13" width="13.6640625" customWidth="1"/>
-    <col min="14" max="14" width="13.83203125" customWidth="1"/>
-    <col min="15" max="16" width="13.5" customWidth="1"/>
-    <col min="17" max="17" width="14.33203125" customWidth="1"/>
+    <col min="10" max="10" width="17.28515625" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" customWidth="1"/>
+    <col min="12" max="13" width="13.7109375" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" customWidth="1"/>
+    <col min="15" max="16" width="13.42578125" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:17" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="384" t="s">
         <v>477</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A3" s="385" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>482</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="E7" s="242" t="s">
         <v>272</v>
       </c>
@@ -74874,7 +74874,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="7" t="s">
         <v>309</v>
       </c>
@@ -74940,7 +74940,7 @@
         <v>53071445.155000001</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="7"/>
       <c r="B10" s="248" t="s">
         <v>71</v>
@@ -75004,7 +75004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A11" s="7"/>
       <c r="B11" s="248"/>
       <c r="C11" s="200"/>
@@ -75062,7 +75062,7 @@
         <v>53071445.155000001</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A12" s="7" t="s">
         <v>310</v>
       </c>
@@ -75128,7 +75128,7 @@
         <v>11298424.716666667</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A13" s="6"/>
       <c r="B13" s="248" t="s">
         <v>20</v>
@@ -75192,7 +75192,7 @@
         <v>36384778.34375</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A14" s="6"/>
       <c r="B14" s="248" t="s">
         <v>20</v>
@@ -75256,7 +75256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A15" s="6"/>
       <c r="B15" s="248" t="s">
         <v>18</v>
@@ -75320,7 +75320,7 @@
         <v>3441912.2708333335</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A16" s="6"/>
       <c r="B16" s="248" t="s">
         <v>311</v>
@@ -75384,7 +75384,7 @@
         <v>1946329.82375</v>
       </c>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="6"/>
       <c r="B17" s="200"/>
       <c r="C17" s="200"/>
@@ -75442,7 +75442,7 @@
         <v>53071445.155000001</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C20" s="6" t="s">
         <v>483</v>
       </c>
@@ -75462,7 +75462,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C22" s="6" t="s">
         <v>13</v>
       </c>
@@ -75489,7 +75489,7 @@
         <v>17934062500</v>
       </c>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C23" s="6" t="s">
         <v>6</v>
       </c>
@@ -75518,7 +75518,7 @@
         <v>1946853005.5725641</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C24" s="6" t="s">
         <v>372</v>
       </c>
@@ -75547,7 +75547,7 @@
         <v>21319022.458333254</v>
       </c>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C25" s="6" t="s">
         <v>373</v>
       </c>
@@ -75576,7 +75576,7 @@
         <v>43289890.595833302</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C26" s="6" t="s">
         <v>5</v>
       </c>
@@ -75605,7 +75605,7 @@
         <v>1705924209.0833335</v>
       </c>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="E27" s="6"/>
       <c r="F27" s="6"/>
       <c r="G27" s="6"/>
@@ -75613,7 +75613,7 @@
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="E28" s="321">
         <f>SUM(E22:E27)</f>
         <v>28049769787.080002</v>
@@ -75639,7 +75639,7 @@
         <v>21651448627.71006</v>
       </c>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="F30" s="320">
         <f>+E9+E10</f>
         <v>656800101.02076912</v>
